--- a/f_total_cap_nhat.xlsx
+++ b/f_total_cap_nhat.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,56 +425,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tỉnh</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Loại</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tổng giao</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Đầu kỳ CMT</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Đầu kỳ yếu thế</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Đầu kỳ còn lại</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TH ngày 18</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>KH giao</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>KH ngày</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>KQ đã TH</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>KH còn lại</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Lũy kế TH</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
@@ -482,26 +514,34 @@
       <c r="C2" t="n">
         <v>1079493</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>298044</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33269</v>
+      </c>
+      <c r="H2" t="n">
         <v>231171</v>
       </c>
-      <c r="E2" t="n">
+      <c r="I2" t="n">
         <v>13679</v>
       </c>
-      <c r="F2" t="n">
+      <c r="J2" t="n">
         <v>80702</v>
       </c>
-      <c r="G2" t="n">
+      <c r="K2" t="n">
         <v>150469</v>
       </c>
-      <c r="H2" t="n">
-        <v>23189</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4316</v>
-      </c>
-      <c r="J2" t="n">
-        <v>18873</v>
+      <c r="L2" t="n">
+        <v>42350</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8740</v>
+      </c>
+      <c r="N2" t="n">
+        <v>33610</v>
       </c>
     </row>
     <row r="3">
@@ -518,26 +558,34 @@
       <c r="C3" t="n">
         <v>1285128</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>419726</v>
+      </c>
+      <c r="G3" t="n">
+        <v>86085</v>
+      </c>
+      <c r="H3" t="n">
         <v>275954</v>
       </c>
-      <c r="E3" t="n">
+      <c r="I3" t="n">
         <v>7402.545454545455</v>
       </c>
-      <c r="F3" t="n">
+      <c r="J3" t="n">
         <v>194526</v>
       </c>
-      <c r="G3" t="n">
+      <c r="K3" t="n">
         <v>81428</v>
       </c>
-      <c r="H3" t="n">
-        <v>40425</v>
-      </c>
-      <c r="I3" t="n">
-        <v>14225</v>
-      </c>
-      <c r="J3" t="n">
-        <v>26200</v>
+      <c r="L3" t="n">
+        <v>70260</v>
+      </c>
+      <c r="M3" t="n">
+        <v>26121</v>
+      </c>
+      <c r="N3" t="n">
+        <v>44139</v>
       </c>
     </row>
     <row r="4">
@@ -554,26 +602,34 @@
       <c r="C4" t="n">
         <v>183942</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>30112</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14085</v>
+      </c>
+      <c r="H4" t="n">
         <v>39843</v>
       </c>
-      <c r="E4" t="n">
+      <c r="I4" t="n">
         <v>1701.181818181818</v>
       </c>
-      <c r="F4" t="n">
+      <c r="J4" t="n">
         <v>21130</v>
       </c>
-      <c r="G4" t="n">
+      <c r="K4" t="n">
         <v>18713</v>
       </c>
-      <c r="H4" t="n">
-        <v>6389</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1066</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5323</v>
+      <c r="L4" t="n">
+        <v>12792</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2155</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10637</v>
       </c>
     </row>
     <row r="5">
@@ -590,26 +646,34 @@
       <c r="C5" t="n">
         <v>294606</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>76246</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9460</v>
+      </c>
+      <c r="H5" t="n">
         <v>64997</v>
       </c>
-      <c r="E5" t="n">
+      <c r="I5" t="n">
         <v>3855.272727272727</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>22589</v>
       </c>
-      <c r="G5" t="n">
+      <c r="K5" t="n">
         <v>42408</v>
       </c>
-      <c r="H5" t="n">
-        <v>7517</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1827</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5690</v>
+      <c r="L5" t="n">
+        <v>16345</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4236</v>
+      </c>
+      <c r="N5" t="n">
+        <v>12109</v>
       </c>
     </row>
     <row r="6">
@@ -626,26 +690,34 @@
       <c r="C6" t="n">
         <v>853784</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>257665</v>
+      </c>
+      <c r="G6" t="n">
+        <v>26774</v>
+      </c>
+      <c r="H6" t="n">
         <v>183356</v>
       </c>
-      <c r="E6" t="n">
+      <c r="I6" t="n">
         <v>10676.27272727273</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>65917</v>
       </c>
-      <c r="G6" t="n">
+      <c r="K6" t="n">
         <v>117439</v>
       </c>
-      <c r="H6" t="n">
-        <v>22928</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4585</v>
-      </c>
-      <c r="J6" t="n">
-        <v>18343</v>
+      <c r="L6" t="n">
+        <v>46160</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10319</v>
+      </c>
+      <c r="N6" t="n">
+        <v>35841</v>
       </c>
     </row>
     <row r="7">
@@ -662,26 +734,34 @@
       <c r="C7" t="n">
         <v>145885</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>42222</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6199</v>
+      </c>
+      <c r="H7" t="n">
         <v>32296</v>
       </c>
-      <c r="E7" t="n">
+      <c r="I7" t="n">
         <v>1734.181818181818</v>
       </c>
-      <c r="F7" t="n">
+      <c r="J7" t="n">
         <v>13220</v>
       </c>
-      <c r="G7" t="n">
+      <c r="K7" t="n">
         <v>19076</v>
       </c>
-      <c r="H7" t="n">
-        <v>2358</v>
-      </c>
-      <c r="I7" t="n">
-        <v>342</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2016</v>
+      <c r="L7" t="n">
+        <v>6328</v>
+      </c>
+      <c r="M7" t="n">
+        <v>902</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5426</v>
       </c>
     </row>
     <row r="8">
@@ -698,26 +778,34 @@
       <c r="C8" t="n">
         <v>865857</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>187915</v>
+      </c>
+      <c r="G8" t="n">
+        <v>60289</v>
+      </c>
+      <c r="H8" t="n">
         <v>185241</v>
       </c>
-      <c r="E8" t="n">
+      <c r="I8" t="n">
         <v>7546.727272727273</v>
       </c>
-      <c r="F8" t="n">
+      <c r="J8" t="n">
         <v>102227</v>
       </c>
-      <c r="G8" t="n">
+      <c r="K8" t="n">
         <v>83014</v>
       </c>
-      <c r="H8" t="n">
-        <v>23460</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4858</v>
-      </c>
-      <c r="J8" t="n">
-        <v>18602</v>
+      <c r="L8" t="n">
+        <v>44892</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9194</v>
+      </c>
+      <c r="N8" t="n">
+        <v>35698</v>
       </c>
     </row>
     <row r="9">
@@ -734,26 +822,34 @@
       <c r="C9" t="n">
         <v>645765</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>172446</v>
+      </c>
+      <c r="G9" t="n">
+        <v>36956</v>
+      </c>
+      <c r="H9" t="n">
         <v>138279</v>
       </c>
-      <c r="E9" t="n">
+      <c r="I9" t="n">
         <v>5918.818181818182</v>
       </c>
-      <c r="F9" t="n">
+      <c r="J9" t="n">
         <v>73172</v>
       </c>
-      <c r="G9" t="n">
+      <c r="K9" t="n">
         <v>65107</v>
       </c>
-      <c r="H9" t="n">
-        <v>17515</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4897</v>
-      </c>
-      <c r="J9" t="n">
-        <v>12618</v>
+      <c r="L9" t="n">
+        <v>32932</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9499</v>
+      </c>
+      <c r="N9" t="n">
+        <v>23433</v>
       </c>
     </row>
     <row r="10">
@@ -770,26 +866,34 @@
       <c r="C10" t="n">
         <v>1409894</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>425517</v>
+      </c>
+      <c r="G10" t="n">
+        <v>75045</v>
+      </c>
+      <c r="H10" t="n">
         <v>301559</v>
       </c>
-      <c r="E10" t="n">
+      <c r="I10" t="n">
         <v>13768.27272727273</v>
       </c>
-      <c r="F10" t="n">
+      <c r="J10" t="n">
         <v>150108</v>
       </c>
-      <c r="G10" t="n">
+      <c r="K10" t="n">
         <v>151451</v>
       </c>
-      <c r="H10" t="n">
-        <v>34483</v>
-      </c>
-      <c r="I10" t="n">
-        <v>10423</v>
-      </c>
-      <c r="J10" t="n">
-        <v>24060</v>
+      <c r="L10" t="n">
+        <v>61307</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19113</v>
+      </c>
+      <c r="N10" t="n">
+        <v>42194</v>
       </c>
     </row>
     <row r="11">
@@ -806,26 +910,34 @@
       <c r="C11" t="n">
         <v>1007603</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>274111</v>
+      </c>
+      <c r="G11" t="n">
+        <v>43552</v>
+      </c>
+      <c r="H11" t="n">
         <v>214388</v>
       </c>
-      <c r="E11" t="n">
+      <c r="I11" t="n">
         <v>11592.45454545455</v>
       </c>
-      <c r="F11" t="n">
+      <c r="J11" t="n">
         <v>86871</v>
       </c>
-      <c r="G11" t="n">
+      <c r="K11" t="n">
         <v>127517</v>
       </c>
-      <c r="H11" t="n">
-        <v>23018</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>18017</v>
+      <c r="L11" t="n">
+        <v>41698</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9421</v>
+      </c>
+      <c r="N11" t="n">
+        <v>32277</v>
       </c>
     </row>
     <row r="12">
@@ -842,26 +954,34 @@
       <c r="C12" t="n">
         <v>1084925</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>258292</v>
+      </c>
+      <c r="G12" t="n">
+        <v>61332</v>
+      </c>
+      <c r="H12" t="n">
         <v>232427</v>
       </c>
-      <c r="E12" t="n">
+      <c r="I12" t="n">
         <v>11115.09090909091</v>
       </c>
-      <c r="F12" t="n">
+      <c r="J12" t="n">
         <v>110161</v>
       </c>
-      <c r="G12" t="n">
+      <c r="K12" t="n">
         <v>122266</v>
       </c>
-      <c r="H12" t="n">
-        <v>25615</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4610</v>
-      </c>
-      <c r="J12" t="n">
-        <v>21005</v>
+      <c r="L12" t="n">
+        <v>51315</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8936</v>
+      </c>
+      <c r="N12" t="n">
+        <v>42379</v>
       </c>
     </row>
     <row r="13">
@@ -878,26 +998,34 @@
       <c r="C13" t="n">
         <v>3578511</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>1393293</v>
+      </c>
+      <c r="G13" t="n">
+        <v>135141</v>
+      </c>
+      <c r="H13" t="n">
         <v>766690</v>
       </c>
-      <c r="E13" t="n">
+      <c r="I13" t="n">
         <v>36311.36363636364</v>
       </c>
-      <c r="F13" t="n">
+      <c r="J13" t="n">
         <v>367265</v>
       </c>
-      <c r="G13" t="n">
+      <c r="K13" t="n">
         <v>399425</v>
       </c>
-      <c r="H13" t="n">
-        <v>75897</v>
-      </c>
-      <c r="I13" t="n">
-        <v>36660</v>
-      </c>
-      <c r="J13" t="n">
-        <v>39237</v>
+      <c r="L13" t="n">
+        <v>133518</v>
+      </c>
+      <c r="M13" t="n">
+        <v>67237</v>
+      </c>
+      <c r="N13" t="n">
+        <v>66281</v>
       </c>
     </row>
     <row r="14">
@@ -914,26 +1042,34 @@
       <c r="C14" t="n">
         <v>3265949</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>1559361</v>
+      </c>
+      <c r="G14" t="n">
+        <v>122051</v>
+      </c>
+      <c r="H14" t="n">
         <v>699078</v>
       </c>
-      <c r="E14" t="n">
+      <c r="I14" t="n">
         <v>24981.36363636364</v>
       </c>
-      <c r="F14" t="n">
+      <c r="J14" t="n">
         <v>424283</v>
       </c>
-      <c r="G14" t="n">
+      <c r="K14" t="n">
         <v>274795</v>
       </c>
-      <c r="H14" t="n">
-        <v>81703</v>
-      </c>
-      <c r="I14" t="n">
-        <v>37794</v>
-      </c>
-      <c r="J14" t="n">
-        <v>43909</v>
+      <c r="L14" t="n">
+        <v>153137</v>
+      </c>
+      <c r="M14" t="n">
+        <v>71410</v>
+      </c>
+      <c r="N14" t="n">
+        <v>81727</v>
       </c>
     </row>
     <row r="15">
@@ -950,26 +1086,34 @@
       <c r="C15" t="n">
         <v>1044956</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>424815</v>
+      </c>
+      <c r="G15" t="n">
+        <v>49488</v>
+      </c>
+      <c r="H15" t="n">
         <v>224183</v>
       </c>
-      <c r="E15" t="n">
+      <c r="I15" t="n">
         <v>7320.909090909091</v>
       </c>
-      <c r="F15" t="n">
+      <c r="J15" t="n">
         <v>143653</v>
       </c>
-      <c r="G15" t="n">
+      <c r="K15" t="n">
         <v>80530</v>
       </c>
-      <c r="H15" t="n">
-        <v>24150</v>
-      </c>
-      <c r="I15" t="n">
-        <v>8355</v>
-      </c>
-      <c r="J15" t="n">
-        <v>15795</v>
+      <c r="L15" t="n">
+        <v>46045</v>
+      </c>
+      <c r="M15" t="n">
+        <v>15631</v>
+      </c>
+      <c r="N15" t="n">
+        <v>30414</v>
       </c>
     </row>
     <row r="16">
@@ -986,26 +1130,34 @@
       <c r="C16" t="n">
         <v>361645</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>87356</v>
+      </c>
+      <c r="G16" t="n">
+        <v>28585</v>
+      </c>
+      <c r="H16" t="n">
         <v>77637</v>
       </c>
-      <c r="E16" t="n">
+      <c r="I16" t="n">
         <v>1452.272727272727</v>
       </c>
-      <c r="F16" t="n">
+      <c r="J16" t="n">
         <v>61662</v>
       </c>
-      <c r="G16" t="n">
+      <c r="K16" t="n">
         <v>15975</v>
       </c>
-      <c r="H16" t="n">
-        <v>21702</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2562</v>
-      </c>
-      <c r="J16" t="n">
-        <v>19140</v>
+      <c r="L16" t="n">
+        <v>35414</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4943</v>
+      </c>
+      <c r="N16" t="n">
+        <v>30471</v>
       </c>
     </row>
     <row r="17">
@@ -1022,26 +1174,34 @@
       <c r="C17" t="n">
         <v>285109</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>75597</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18705</v>
+      </c>
+      <c r="H17" t="n">
         <v>61076</v>
       </c>
-      <c r="E17" t="n">
+      <c r="I17" t="n">
         <v>2414.909090909091</v>
       </c>
-      <c r="F17" t="n">
+      <c r="J17" t="n">
         <v>34512</v>
       </c>
-      <c r="G17" t="n">
+      <c r="K17" t="n">
         <v>26564</v>
       </c>
-      <c r="H17" t="n">
-        <v>8842</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2290</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6552</v>
+      <c r="L17" t="n">
+        <v>17192</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4505</v>
+      </c>
+      <c r="N17" t="n">
+        <v>12687</v>
       </c>
     </row>
     <row r="18">
@@ -1058,26 +1218,34 @@
       <c r="C18" t="n">
         <v>894371</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>338319</v>
+      </c>
+      <c r="G18" t="n">
+        <v>52801</v>
+      </c>
+      <c r="H18" t="n">
         <v>190950</v>
       </c>
-      <c r="E18" t="n">
+      <c r="I18" t="n">
         <v>6069.454545454545</v>
       </c>
-      <c r="F18" t="n">
+      <c r="J18" t="n">
         <v>124186</v>
       </c>
-      <c r="G18" t="n">
+      <c r="K18" t="n">
         <v>66764</v>
       </c>
-      <c r="H18" t="n">
-        <v>24010</v>
-      </c>
-      <c r="I18" t="n">
-        <v>6595</v>
-      </c>
-      <c r="J18" t="n">
-        <v>17415</v>
+      <c r="L18" t="n">
+        <v>44687</v>
+      </c>
+      <c r="M18" t="n">
+        <v>12537</v>
+      </c>
+      <c r="N18" t="n">
+        <v>32150</v>
       </c>
     </row>
     <row r="19">
@@ -1094,26 +1262,34 @@
       <c r="C19" t="n">
         <v>565397</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>129712</v>
+      </c>
+      <c r="G19" t="n">
+        <v>36512</v>
+      </c>
+      <c r="H19" t="n">
         <v>120456</v>
       </c>
-      <c r="E19" t="n">
+      <c r="I19" t="n">
         <v>5021</v>
       </c>
-      <c r="F19" t="n">
+      <c r="J19" t="n">
         <v>65225</v>
       </c>
-      <c r="G19" t="n">
+      <c r="K19" t="n">
         <v>55231</v>
       </c>
-      <c r="H19" t="n">
-        <v>17618</v>
-      </c>
-      <c r="I19" t="n">
-        <v>4100</v>
-      </c>
-      <c r="J19" t="n">
-        <v>13518</v>
+      <c r="L19" t="n">
+        <v>29959</v>
+      </c>
+      <c r="M19" t="n">
+        <v>7729</v>
+      </c>
+      <c r="N19" t="n">
+        <v>22230</v>
       </c>
     </row>
     <row r="20">
@@ -1130,26 +1306,34 @@
       <c r="C20" t="n">
         <v>526562</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>127241</v>
+      </c>
+      <c r="G20" t="n">
+        <v>28925</v>
+      </c>
+      <c r="H20" t="n">
         <v>113964</v>
       </c>
-      <c r="E20" t="n">
+      <c r="I20" t="n">
         <v>5339.727272727273</v>
       </c>
-      <c r="F20" t="n">
+      <c r="J20" t="n">
         <v>55227</v>
       </c>
-      <c r="G20" t="n">
+      <c r="K20" t="n">
         <v>58737</v>
       </c>
-      <c r="H20" t="n">
-        <v>12799</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3192</v>
-      </c>
-      <c r="J20" t="n">
-        <v>9607</v>
+      <c r="L20" t="n">
+        <v>24513</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6226</v>
+      </c>
+      <c r="N20" t="n">
+        <v>18287</v>
       </c>
     </row>
     <row r="21">
@@ -1166,26 +1350,34 @@
       <c r="C21" t="n">
         <v>162492</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>36211</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4271</v>
+      </c>
+      <c r="H21" t="n">
         <v>35928</v>
       </c>
-      <c r="E21" t="n">
+      <c r="I21" t="n">
         <v>2216.545454545455</v>
       </c>
-      <c r="F21" t="n">
+      <c r="J21" t="n">
         <v>11546</v>
       </c>
-      <c r="G21" t="n">
+      <c r="K21" t="n">
         <v>24382</v>
       </c>
-      <c r="H21" t="n">
-        <v>3342</v>
-      </c>
-      <c r="I21" t="n">
-        <v>755</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2587</v>
+      <c r="L21" t="n">
+        <v>8347</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2130</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6217</v>
       </c>
     </row>
     <row r="22">
@@ -1202,26 +1394,34 @@
       <c r="C22" t="n">
         <v>1188375</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>281213</v>
+      </c>
+      <c r="G22" t="n">
+        <v>49983</v>
+      </c>
+      <c r="H22" t="n">
         <v>254618</v>
       </c>
-      <c r="E22" t="n">
+      <c r="I22" t="n">
         <v>13839</v>
       </c>
-      <c r="F22" t="n">
+      <c r="J22" t="n">
         <v>102389</v>
       </c>
-      <c r="G22" t="n">
+      <c r="K22" t="n">
         <v>152229</v>
       </c>
-      <c r="H22" t="n">
-        <v>27828</v>
-      </c>
-      <c r="I22" t="n">
-        <v>6664</v>
-      </c>
-      <c r="J22" t="n">
-        <v>21164</v>
+      <c r="L22" t="n">
+        <v>51459</v>
+      </c>
+      <c r="M22" t="n">
+        <v>12983</v>
+      </c>
+      <c r="N22" t="n">
+        <v>38476</v>
       </c>
     </row>
     <row r="23">
@@ -1238,26 +1438,34 @@
       <c r="C23" t="n">
         <v>371038</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>88344</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20848</v>
+      </c>
+      <c r="H23" t="n">
         <v>79486</v>
       </c>
-      <c r="E23" t="n">
+      <c r="I23" t="n">
         <v>3715.181818181818</v>
       </c>
-      <c r="F23" t="n">
+      <c r="J23" t="n">
         <v>38619</v>
       </c>
-      <c r="G23" t="n">
+      <c r="K23" t="n">
         <v>40867</v>
       </c>
-      <c r="H23" t="n">
-        <v>10183</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2351</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7832</v>
+      <c r="L23" t="n">
+        <v>19168</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4317</v>
+      </c>
+      <c r="N23" t="n">
+        <v>14851</v>
       </c>
     </row>
     <row r="24">
@@ -1274,26 +1482,34 @@
       <c r="C24" t="n">
         <v>1017106</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>245892</v>
+      </c>
+      <c r="G24" t="n">
+        <v>68931</v>
+      </c>
+      <c r="H24" t="n">
         <v>217875</v>
       </c>
-      <c r="E24" t="n">
+      <c r="I24" t="n">
         <v>8072.545454545455</v>
       </c>
-      <c r="F24" t="n">
+      <c r="J24" t="n">
         <v>129077</v>
       </c>
-      <c r="G24" t="n">
+      <c r="K24" t="n">
         <v>88798</v>
       </c>
-      <c r="H24" t="n">
-        <v>26983</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6039</v>
-      </c>
-      <c r="J24" t="n">
-        <v>20944</v>
+      <c r="L24" t="n">
+        <v>61172</v>
+      </c>
+      <c r="M24" t="n">
+        <v>12732</v>
+      </c>
+      <c r="N24" t="n">
+        <v>48440</v>
       </c>
     </row>
     <row r="25">
@@ -1310,26 +1526,34 @@
       <c r="C25" t="n">
         <v>914401</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>341001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>49929</v>
+      </c>
+      <c r="H25" t="n">
         <v>195226</v>
       </c>
-      <c r="E25" t="n">
+      <c r="I25" t="n">
         <v>7872.727272727273</v>
       </c>
-      <c r="F25" t="n">
+      <c r="J25" t="n">
         <v>108626</v>
       </c>
-      <c r="G25" t="n">
+      <c r="K25" t="n">
         <v>86600</v>
       </c>
-      <c r="H25" t="n">
-        <v>20088</v>
-      </c>
-      <c r="I25" t="n">
-        <v>6694</v>
-      </c>
-      <c r="J25" t="n">
-        <v>13394</v>
+      <c r="L25" t="n">
+        <v>38791</v>
+      </c>
+      <c r="M25" t="n">
+        <v>12737</v>
+      </c>
+      <c r="N25" t="n">
+        <v>26054</v>
       </c>
     </row>
     <row r="26">
@@ -1346,26 +1570,34 @@
       <c r="C26" t="n">
         <v>1261095</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>387874</v>
+      </c>
+      <c r="G26" t="n">
+        <v>83582</v>
+      </c>
+      <c r="H26" t="n">
         <v>269506</v>
       </c>
-      <c r="E26" t="n">
+      <c r="I26" t="n">
         <v>8691.363636363636</v>
       </c>
-      <c r="F26" t="n">
+      <c r="J26" t="n">
         <v>173901</v>
       </c>
-      <c r="G26" t="n">
+      <c r="K26" t="n">
         <v>95605</v>
       </c>
-      <c r="H26" t="n">
-        <v>32419</v>
-      </c>
-      <c r="I26" t="n">
-        <v>9730</v>
-      </c>
-      <c r="J26" t="n">
-        <v>22689</v>
+      <c r="L26" t="n">
+        <v>60203</v>
+      </c>
+      <c r="M26" t="n">
+        <v>18146</v>
+      </c>
+      <c r="N26" t="n">
+        <v>42057</v>
       </c>
     </row>
     <row r="27">
@@ -1382,26 +1614,34 @@
       <c r="C27" t="n">
         <v>416872</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>160366</v>
+      </c>
+      <c r="G27" t="n">
+        <v>19902</v>
+      </c>
+      <c r="H27" t="n">
         <v>89232</v>
       </c>
-      <c r="E27" t="n">
+      <c r="I27" t="n">
         <v>3199.727272727273</v>
       </c>
-      <c r="F27" t="n">
+      <c r="J27" t="n">
         <v>54035</v>
       </c>
-      <c r="G27" t="n">
+      <c r="K27" t="n">
         <v>35197</v>
       </c>
-      <c r="H27" t="n">
-        <v>12119</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3346</v>
-      </c>
-      <c r="J27" t="n">
-        <v>8773</v>
+      <c r="L27" t="n">
+        <v>22220</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6106</v>
+      </c>
+      <c r="N27" t="n">
+        <v>16114</v>
       </c>
     </row>
     <row r="28">
@@ -1418,26 +1658,34 @@
       <c r="C28" t="n">
         <v>576110</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>130368</v>
+      </c>
+      <c r="G28" t="n">
+        <v>42884</v>
+      </c>
+      <c r="H28" t="n">
         <v>123576</v>
       </c>
-      <c r="E28" t="n">
+      <c r="I28" t="n">
         <v>4800</v>
       </c>
-      <c r="F28" t="n">
+      <c r="J28" t="n">
         <v>70776</v>
       </c>
-      <c r="G28" t="n">
+      <c r="K28" t="n">
         <v>52800</v>
       </c>
-      <c r="H28" t="n">
-        <v>19205</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2730</v>
-      </c>
-      <c r="J28" t="n">
-        <v>16475</v>
+      <c r="L28" t="n">
+        <v>34416</v>
+      </c>
+      <c r="M28" t="n">
+        <v>5186</v>
+      </c>
+      <c r="N28" t="n">
+        <v>29230</v>
       </c>
     </row>
     <row r="29">
@@ -1454,26 +1702,34 @@
       <c r="C29" t="n">
         <v>322028</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>86131</v>
+      </c>
+      <c r="G29" t="n">
+        <v>17942</v>
+      </c>
+      <c r="H29" t="n">
         <v>69184</v>
       </c>
-      <c r="E29" t="n">
+      <c r="I29" t="n">
         <v>3099.363636363636</v>
       </c>
-      <c r="F29" t="n">
+      <c r="J29" t="n">
         <v>35091</v>
       </c>
-      <c r="G29" t="n">
+      <c r="K29" t="n">
         <v>34093</v>
       </c>
-      <c r="H29" t="n">
-        <v>9303</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1502</v>
-      </c>
-      <c r="J29" t="n">
-        <v>7801</v>
+      <c r="L29" t="n">
+        <v>19779</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3167</v>
+      </c>
+      <c r="N29" t="n">
+        <v>16612</v>
       </c>
     </row>
     <row r="30">
@@ -1490,26 +1746,34 @@
       <c r="C30" t="n">
         <v>472333</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>112163</v>
+      </c>
+      <c r="G30" t="n">
+        <v>20557</v>
+      </c>
+      <c r="H30" t="n">
         <v>102301</v>
       </c>
-      <c r="E30" t="n">
+      <c r="I30" t="n">
         <v>5410.818181818182</v>
       </c>
-      <c r="F30" t="n">
+      <c r="J30" t="n">
         <v>42782</v>
       </c>
-      <c r="G30" t="n">
+      <c r="K30" t="n">
         <v>59519</v>
       </c>
-      <c r="H30" t="n">
-        <v>10966</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1716</v>
-      </c>
-      <c r="J30" t="n">
-        <v>9250</v>
+      <c r="L30" t="n">
+        <v>20885</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3529</v>
+      </c>
+      <c r="N30" t="n">
+        <v>17356</v>
       </c>
     </row>
     <row r="31">
@@ -1526,26 +1790,34 @@
       <c r="C31" t="n">
         <v>978536</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>312801</v>
+      </c>
+      <c r="G31" t="n">
+        <v>45959</v>
+      </c>
+      <c r="H31" t="n">
         <v>209020</v>
       </c>
-      <c r="E31" t="n">
+      <c r="I31" t="n">
         <v>10110.45454545455</v>
       </c>
-      <c r="F31" t="n">
+      <c r="J31" t="n">
         <v>97805</v>
       </c>
-      <c r="G31" t="n">
+      <c r="K31" t="n">
         <v>111215</v>
       </c>
-      <c r="H31" t="n">
-        <v>20863</v>
-      </c>
-      <c r="I31" t="n">
-        <v>4653</v>
-      </c>
-      <c r="J31" t="n">
-        <v>16210</v>
+      <c r="L31" t="n">
+        <v>41055</v>
+      </c>
+      <c r="M31" t="n">
+        <v>9089</v>
+      </c>
+      <c r="N31" t="n">
+        <v>31966</v>
       </c>
     </row>
     <row r="32">
@@ -1562,26 +1834,34 @@
       <c r="C32" t="n">
         <v>1009008</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>342337</v>
+      </c>
+      <c r="G32" t="n">
+        <v>33008</v>
+      </c>
+      <c r="H32" t="n">
         <v>215467</v>
       </c>
-      <c r="E32" t="n">
+      <c r="I32" t="n">
         <v>12329.09090909091</v>
       </c>
-      <c r="F32" t="n">
+      <c r="J32" t="n">
         <v>79847</v>
       </c>
-      <c r="G32" t="n">
+      <c r="K32" t="n">
         <v>135620</v>
       </c>
-      <c r="H32" t="n">
-        <v>25932</v>
-      </c>
-      <c r="I32" t="n">
-        <v>5876</v>
-      </c>
-      <c r="J32" t="n">
-        <v>20056</v>
+      <c r="L32" t="n">
+        <v>45519</v>
+      </c>
+      <c r="M32" t="n">
+        <v>10745</v>
+      </c>
+      <c r="N32" t="n">
+        <v>34774</v>
       </c>
     </row>
     <row r="33">
@@ -1598,26 +1878,34 @@
       <c r="C33" t="n">
         <v>598334</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>170531</v>
+      </c>
+      <c r="G33" t="n">
+        <v>42826</v>
+      </c>
+      <c r="H33" t="n">
         <v>128017</v>
       </c>
-      <c r="E33" t="n">
+      <c r="I33" t="n">
         <v>4191.636363636364</v>
       </c>
-      <c r="F33" t="n">
+      <c r="J33" t="n">
         <v>81909</v>
       </c>
-      <c r="G33" t="n">
+      <c r="K33" t="n">
         <v>46108</v>
       </c>
-      <c r="H33" t="n">
-        <v>16290</v>
-      </c>
-      <c r="I33" t="n">
-        <v>5236</v>
-      </c>
-      <c r="J33" t="n">
-        <v>11054</v>
+      <c r="L33" t="n">
+        <v>31495</v>
+      </c>
+      <c r="M33" t="n">
+        <v>9869</v>
+      </c>
+      <c r="N33" t="n">
+        <v>21626</v>
       </c>
     </row>
     <row r="34">
@@ -1634,26 +1922,34 @@
       <c r="C34" t="n">
         <v>619422</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>150535</v>
+      </c>
+      <c r="G34" t="n">
+        <v>30397</v>
+      </c>
+      <c r="H34" t="n">
         <v>133210</v>
       </c>
-      <c r="E34" t="n">
+      <c r="I34" t="n">
         <v>6730.454545454545</v>
       </c>
-      <c r="F34" t="n">
+      <c r="J34" t="n">
         <v>59175</v>
       </c>
-      <c r="G34" t="n">
+      <c r="K34" t="n">
         <v>74035</v>
       </c>
-      <c r="H34" t="n">
-        <v>17696</v>
-      </c>
-      <c r="I34" t="n">
-        <v>3496</v>
-      </c>
-      <c r="J34" t="n">
-        <v>14200</v>
+      <c r="L34" t="n">
+        <v>33050</v>
+      </c>
+      <c r="M34" t="n">
+        <v>6619</v>
+      </c>
+      <c r="N34" t="n">
+        <v>26431</v>
       </c>
     </row>
     <row r="35">
@@ -1670,26 +1966,34 @@
       <c r="C35" t="n">
         <v>1040674</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>292375</v>
+      </c>
+      <c r="G35" t="n">
+        <v>43472</v>
+      </c>
+      <c r="H35" t="n">
         <v>221968</v>
       </c>
-      <c r="E35" t="n">
+      <c r="I35" t="n">
         <v>12219.18181818182</v>
       </c>
-      <c r="F35" t="n">
+      <c r="J35" t="n">
         <v>87557</v>
       </c>
-      <c r="G35" t="n">
+      <c r="K35" t="n">
         <v>134411</v>
       </c>
-      <c r="H35" t="n">
-        <v>26906</v>
-      </c>
-      <c r="I35" t="n">
-        <v>4407</v>
-      </c>
-      <c r="J35" t="n">
-        <v>22499</v>
+      <c r="L35" t="n">
+        <v>44430</v>
+      </c>
+      <c r="M35" t="n">
+        <v>8181</v>
+      </c>
+      <c r="N35" t="n">
+        <v>36249</v>
       </c>
     </row>
     <row r="36">
@@ -1707,25 +2011,33 @@
         <v>777063</v>
       </c>
       <c r="D36" t="n">
+        <v>463874</v>
+      </c>
+      <c r="E36" t="n">
+        <v>313189</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
         <v>127144</v>
       </c>
-      <c r="E36" t="n">
+      <c r="I36" t="n">
         <v>8534.09090909091</v>
       </c>
-      <c r="F36" t="n">
+      <c r="J36" t="n">
         <v>33269</v>
       </c>
-      <c r="G36" t="n">
+      <c r="K36" t="n">
         <v>93875</v>
       </c>
-      <c r="H36" t="n">
-        <v>19307</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2873</v>
-      </c>
-      <c r="J36" t="n">
-        <v>16434</v>
+      <c r="L36" t="n">
+        <v>34235</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5872</v>
+      </c>
+      <c r="N36" t="n">
+        <v>28363</v>
       </c>
     </row>
     <row r="37">
@@ -1743,25 +2055,33 @@
         <v>855156</v>
       </c>
       <c r="D37" t="n">
+        <v>625314</v>
+      </c>
+      <c r="E37" t="n">
+        <v>229842</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
         <v>151775</v>
       </c>
-      <c r="E37" t="n">
+      <c r="I37" t="n">
         <v>5971.818181818182</v>
       </c>
-      <c r="F37" t="n">
+      <c r="J37" t="n">
         <v>86085</v>
       </c>
-      <c r="G37" t="n">
+      <c r="K37" t="n">
         <v>65690</v>
       </c>
-      <c r="H37" t="n">
-        <v>32136</v>
-      </c>
-      <c r="I37" t="n">
-        <v>9270</v>
-      </c>
-      <c r="J37" t="n">
-        <v>22866</v>
+      <c r="L37" t="n">
+        <v>54545</v>
+      </c>
+      <c r="M37" t="n">
+        <v>17052</v>
+      </c>
+      <c r="N37" t="n">
+        <v>37493</v>
       </c>
     </row>
     <row r="38">
@@ -1779,25 +2099,33 @@
         <v>153708</v>
       </c>
       <c r="D38" t="n">
+        <v>84115</v>
+      </c>
+      <c r="E38" t="n">
+        <v>69593</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
         <v>21914</v>
       </c>
-      <c r="E38" t="n">
+      <c r="I38" t="n">
         <v>711.7272727272727</v>
       </c>
-      <c r="F38" t="n">
+      <c r="J38" t="n">
         <v>14085</v>
       </c>
-      <c r="G38" t="n">
+      <c r="K38" t="n">
         <v>7829</v>
       </c>
-      <c r="H38" t="n">
-        <v>6062</v>
-      </c>
-      <c r="I38" t="n">
-        <v>956</v>
-      </c>
-      <c r="J38" t="n">
-        <v>5106</v>
+      <c r="L38" t="n">
+        <v>11910</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1896</v>
+      </c>
+      <c r="N38" t="n">
+        <v>10014</v>
       </c>
     </row>
     <row r="39">
@@ -1815,25 +2143,33 @@
         <v>216463</v>
       </c>
       <c r="D39" t="n">
+        <v>101189</v>
+      </c>
+      <c r="E39" t="n">
+        <v>115274</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
         <v>35749</v>
       </c>
-      <c r="E39" t="n">
+      <c r="I39" t="n">
         <v>2389.909090909091</v>
       </c>
-      <c r="F39" t="n">
+      <c r="J39" t="n">
         <v>9460</v>
       </c>
-      <c r="G39" t="n">
+      <c r="K39" t="n">
         <v>26289</v>
       </c>
-      <c r="H39" t="n">
-        <v>6232</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1113</v>
-      </c>
-      <c r="J39" t="n">
-        <v>5119</v>
+      <c r="L39" t="n">
+        <v>13002</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2635</v>
+      </c>
+      <c r="N39" t="n">
+        <v>10367</v>
       </c>
     </row>
     <row r="40">
@@ -1851,25 +2187,33 @@
         <v>590772</v>
       </c>
       <c r="D40" t="n">
+        <v>337445</v>
+      </c>
+      <c r="E40" t="n">
+        <v>253327</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="n">
         <v>100846</v>
       </c>
-      <c r="E40" t="n">
+      <c r="I40" t="n">
         <v>6733.818181818182</v>
       </c>
-      <c r="F40" t="n">
+      <c r="J40" t="n">
         <v>26774</v>
       </c>
-      <c r="G40" t="n">
+      <c r="K40" t="n">
         <v>74072</v>
       </c>
-      <c r="H40" t="n">
-        <v>19006</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2648</v>
-      </c>
-      <c r="J40" t="n">
-        <v>16358</v>
+      <c r="L40" t="n">
+        <v>36929</v>
+      </c>
+      <c r="M40" t="n">
+        <v>6209</v>
+      </c>
+      <c r="N40" t="n">
+        <v>30720</v>
       </c>
     </row>
     <row r="41">
@@ -1887,25 +2231,33 @@
         <v>103347</v>
       </c>
       <c r="D41" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E41" t="n">
+        <v>57109</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="n">
         <v>17763</v>
       </c>
-      <c r="E41" t="n">
+      <c r="I41" t="n">
         <v>1051.272727272727</v>
       </c>
-      <c r="F41" t="n">
+      <c r="J41" t="n">
         <v>6199</v>
       </c>
-      <c r="G41" t="n">
+      <c r="K41" t="n">
         <v>11564</v>
       </c>
-      <c r="H41" t="n">
-        <v>2168</v>
-      </c>
-      <c r="I41" t="n">
-        <v>266</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1902</v>
+      <c r="L41" t="n">
+        <v>5329</v>
+      </c>
+      <c r="M41" t="n">
+        <v>688</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4641</v>
       </c>
     </row>
     <row r="42">
@@ -1923,25 +2275,33 @@
         <v>675934</v>
       </c>
       <c r="D42" t="n">
+        <v>404500</v>
+      </c>
+      <c r="E42" t="n">
+        <v>271434</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
         <v>101883</v>
       </c>
-      <c r="E42" t="n">
+      <c r="I42" t="n">
         <v>3781.272727272727</v>
       </c>
-      <c r="F42" t="n">
+      <c r="J42" t="n">
         <v>60289</v>
       </c>
-      <c r="G42" t="n">
+      <c r="K42" t="n">
         <v>41594</v>
       </c>
-      <c r="H42" t="n">
-        <v>21377</v>
-      </c>
-      <c r="I42" t="n">
-        <v>3948</v>
-      </c>
-      <c r="J42" t="n">
-        <v>17429</v>
+      <c r="L42" t="n">
+        <v>39829</v>
+      </c>
+      <c r="M42" t="n">
+        <v>7396</v>
+      </c>
+      <c r="N42" t="n">
+        <v>32433</v>
       </c>
     </row>
     <row r="43">
@@ -1959,25 +2319,33 @@
         <v>470034</v>
       </c>
       <c r="D43" t="n">
+        <v>280731</v>
+      </c>
+      <c r="E43" t="n">
+        <v>189303</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
         <v>76053</v>
       </c>
-      <c r="E43" t="n">
+      <c r="I43" t="n">
         <v>3554.272727272727</v>
       </c>
-      <c r="F43" t="n">
+      <c r="J43" t="n">
         <v>36956</v>
       </c>
-      <c r="G43" t="n">
+      <c r="K43" t="n">
         <v>39097</v>
       </c>
-      <c r="H43" t="n">
-        <v>14680</v>
-      </c>
-      <c r="I43" t="n">
-        <v>3055</v>
-      </c>
-      <c r="J43" t="n">
-        <v>11625</v>
+      <c r="L43" t="n">
+        <v>27258</v>
+      </c>
+      <c r="M43" t="n">
+        <v>6058</v>
+      </c>
+      <c r="N43" t="n">
+        <v>21200</v>
       </c>
     </row>
     <row r="44">
@@ -1995,25 +2363,33 @@
         <v>977311</v>
       </c>
       <c r="D44" t="n">
+        <v>656794</v>
+      </c>
+      <c r="E44" t="n">
+        <v>320517</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="n">
         <v>165858</v>
       </c>
-      <c r="E44" t="n">
+      <c r="I44" t="n">
         <v>8255.727272727272</v>
       </c>
-      <c r="F44" t="n">
+      <c r="J44" t="n">
         <v>75045</v>
       </c>
-      <c r="G44" t="n">
+      <c r="K44" t="n">
         <v>90813</v>
       </c>
-      <c r="H44" t="n">
-        <v>28651</v>
-      </c>
-      <c r="I44" t="n">
-        <v>6857</v>
-      </c>
-      <c r="J44" t="n">
-        <v>21794</v>
+      <c r="L44" t="n">
+        <v>50407</v>
+      </c>
+      <c r="M44" t="n">
+        <v>12857</v>
+      </c>
+      <c r="N44" t="n">
+        <v>37550</v>
       </c>
     </row>
     <row r="45">
@@ -2031,25 +2407,33 @@
         <v>729187</v>
       </c>
       <c r="D45" t="n">
+        <v>471388</v>
+      </c>
+      <c r="E45" t="n">
+        <v>257799</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="n">
         <v>117914</v>
       </c>
-      <c r="E45" t="n">
+      <c r="I45" t="n">
         <v>6760.181818181818</v>
       </c>
-      <c r="F45" t="n">
+      <c r="J45" t="n">
         <v>43552</v>
       </c>
-      <c r="G45" t="n">
+      <c r="K45" t="n">
         <v>74362</v>
       </c>
-      <c r="H45" t="n">
-        <v>19357</v>
-      </c>
-      <c r="I45" t="n">
-        <v>3368</v>
-      </c>
-      <c r="J45" t="n">
-        <v>15989</v>
+      <c r="L45" t="n">
+        <v>34299</v>
+      </c>
+      <c r="M45" t="n">
+        <v>6462</v>
+      </c>
+      <c r="N45" t="n">
+        <v>27837</v>
       </c>
     </row>
     <row r="46">
@@ -2067,25 +2451,33 @@
         <v>823905</v>
       </c>
       <c r="D46" t="n">
+        <v>494965</v>
+      </c>
+      <c r="E46" t="n">
+        <v>328940</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="n">
         <v>127835</v>
       </c>
-      <c r="E46" t="n">
+      <c r="I46" t="n">
         <v>6045.727272727273</v>
       </c>
-      <c r="F46" t="n">
+      <c r="J46" t="n">
         <v>61332</v>
       </c>
-      <c r="G46" t="n">
+      <c r="K46" t="n">
         <v>66503</v>
       </c>
-      <c r="H46" t="n">
-        <v>23076</v>
-      </c>
-      <c r="I46" t="n">
-        <v>3512</v>
-      </c>
-      <c r="J46" t="n">
-        <v>19564</v>
+      <c r="L46" t="n">
+        <v>45315</v>
+      </c>
+      <c r="M46" t="n">
+        <v>6879</v>
+      </c>
+      <c r="N46" t="n">
+        <v>38436</v>
       </c>
     </row>
     <row r="47">
@@ -2103,25 +2495,33 @@
         <v>2150183</v>
       </c>
       <c r="D47" t="n">
+        <v>1412640</v>
+      </c>
+      <c r="E47" t="n">
+        <v>737543</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="n">
         <v>421680</v>
       </c>
-      <c r="E47" t="n">
+      <c r="I47" t="n">
         <v>26049</v>
       </c>
-      <c r="F47" t="n">
+      <c r="J47" t="n">
         <v>135141</v>
       </c>
-      <c r="G47" t="n">
+      <c r="K47" t="n">
         <v>286539</v>
       </c>
-      <c r="H47" t="n">
-        <v>48482</v>
-      </c>
-      <c r="I47" t="n">
-        <v>17749</v>
-      </c>
-      <c r="J47" t="n">
-        <v>30733</v>
+      <c r="L47" t="n">
+        <v>85359</v>
+      </c>
+      <c r="M47" t="n">
+        <v>35107</v>
+      </c>
+      <c r="N47" t="n">
+        <v>50252</v>
       </c>
     </row>
     <row r="48">
@@ -2139,25 +2539,33 @@
         <v>1663325</v>
       </c>
       <c r="D48" t="n">
+        <v>1085932</v>
+      </c>
+      <c r="E48" t="n">
+        <v>577393</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
         <v>384493</v>
       </c>
-      <c r="E48" t="n">
+      <c r="I48" t="n">
         <v>23858.36363636364</v>
       </c>
-      <c r="F48" t="n">
+      <c r="J48" t="n">
         <v>122051</v>
       </c>
-      <c r="G48" t="n">
+      <c r="K48" t="n">
         <v>262442</v>
       </c>
-      <c r="H48" t="n">
-        <v>47732</v>
-      </c>
-      <c r="I48" t="n">
-        <v>16762</v>
-      </c>
-      <c r="J48" t="n">
-        <v>30970</v>
+      <c r="L48" t="n">
+        <v>88894</v>
+      </c>
+      <c r="M48" t="n">
+        <v>34040</v>
+      </c>
+      <c r="N48" t="n">
+        <v>54854</v>
       </c>
     </row>
     <row r="49">
@@ -2175,25 +2583,33 @@
         <v>610852</v>
       </c>
       <c r="D49" t="n">
+        <v>399689</v>
+      </c>
+      <c r="E49" t="n">
+        <v>211163</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
         <v>123301</v>
       </c>
-      <c r="E49" t="n">
+      <c r="I49" t="n">
         <v>6710.272727272727</v>
       </c>
-      <c r="F49" t="n">
+      <c r="J49" t="n">
         <v>49488</v>
       </c>
-      <c r="G49" t="n">
+      <c r="K49" t="n">
         <v>73813</v>
       </c>
-      <c r="H49" t="n">
-        <v>17107</v>
-      </c>
-      <c r="I49" t="n">
-        <v>4632</v>
-      </c>
-      <c r="J49" t="n">
-        <v>12475</v>
+      <c r="L49" t="n">
+        <v>31779</v>
+      </c>
+      <c r="M49" t="n">
+        <v>8781</v>
+      </c>
+      <c r="N49" t="n">
+        <v>22998</v>
       </c>
     </row>
     <row r="50">
@@ -2211,25 +2627,33 @@
         <v>272950</v>
       </c>
       <c r="D50" t="n">
+        <v>182356</v>
+      </c>
+      <c r="E50" t="n">
+        <v>90594</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
         <v>42700</v>
       </c>
-      <c r="E50" t="n">
+      <c r="I50" t="n">
         <v>1283.181818181818</v>
       </c>
-      <c r="F50" t="n">
+      <c r="J50" t="n">
         <v>28585</v>
       </c>
-      <c r="G50" t="n">
+      <c r="K50" t="n">
         <v>14115</v>
       </c>
-      <c r="H50" t="n">
-        <v>19243</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1886</v>
-      </c>
-      <c r="J50" t="n">
-        <v>17357</v>
+      <c r="L50" t="n">
+        <v>30456</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3575</v>
+      </c>
+      <c r="N50" t="n">
+        <v>26881</v>
       </c>
     </row>
     <row r="51">
@@ -2247,25 +2671,33 @@
         <v>207766</v>
       </c>
       <c r="D51" t="n">
+        <v>141794</v>
+      </c>
+      <c r="E51" t="n">
+        <v>65972</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="n">
         <v>33592</v>
       </c>
-      <c r="E51" t="n">
+      <c r="I51" t="n">
         <v>1353.363636363636</v>
       </c>
-      <c r="F51" t="n">
+      <c r="J51" t="n">
         <v>18705</v>
       </c>
-      <c r="G51" t="n">
+      <c r="K51" t="n">
         <v>14887</v>
       </c>
-      <c r="H51" t="n">
-        <v>7431</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1432</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5999</v>
+      <c r="L51" t="n">
+        <v>14080</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2876</v>
+      </c>
+      <c r="N51" t="n">
+        <v>11204</v>
       </c>
     </row>
     <row r="52">
@@ -2283,25 +2715,33 @@
         <v>549163</v>
       </c>
       <c r="D52" t="n">
+        <v>341243</v>
+      </c>
+      <c r="E52" t="n">
+        <v>207920</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
         <v>105023</v>
       </c>
-      <c r="E52" t="n">
+      <c r="I52" t="n">
         <v>4747.454545454545</v>
       </c>
-      <c r="F52" t="n">
+      <c r="J52" t="n">
         <v>52801</v>
       </c>
-      <c r="G52" t="n">
+      <c r="K52" t="n">
         <v>52222</v>
       </c>
-      <c r="H52" t="n">
-        <v>18151</v>
-      </c>
-      <c r="I52" t="n">
-        <v>3788</v>
-      </c>
-      <c r="J52" t="n">
-        <v>14363</v>
+      <c r="L52" t="n">
+        <v>33343</v>
+      </c>
+      <c r="M52" t="n">
+        <v>7449</v>
+      </c>
+      <c r="N52" t="n">
+        <v>25894</v>
       </c>
     </row>
     <row r="53">
@@ -2319,25 +2759,33 @@
         <v>433574</v>
       </c>
       <c r="D53" t="n">
+        <v>294518</v>
+      </c>
+      <c r="E53" t="n">
+        <v>139056</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="n">
         <v>66251</v>
       </c>
-      <c r="E53" t="n">
+      <c r="I53" t="n">
         <v>2703.545454545455</v>
       </c>
-      <c r="F53" t="n">
+      <c r="J53" t="n">
         <v>36512</v>
       </c>
-      <c r="G53" t="n">
+      <c r="K53" t="n">
         <v>29739</v>
       </c>
-      <c r="H53" t="n">
-        <v>15797</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3135</v>
-      </c>
-      <c r="J53" t="n">
-        <v>12662</v>
+      <c r="L53" t="n">
+        <v>26204</v>
+      </c>
+      <c r="M53" t="n">
+        <v>5877</v>
+      </c>
+      <c r="N53" t="n">
+        <v>20327</v>
       </c>
     </row>
     <row r="54">
@@ -2355,25 +2803,33 @@
         <v>398499</v>
       </c>
       <c r="D54" t="n">
+        <v>203892</v>
+      </c>
+      <c r="E54" t="n">
+        <v>194607</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="n">
         <v>62680</v>
       </c>
-      <c r="E54" t="n">
+      <c r="I54" t="n">
         <v>3068.636363636364</v>
       </c>
-      <c r="F54" t="n">
+      <c r="J54" t="n">
         <v>28925</v>
       </c>
-      <c r="G54" t="n">
+      <c r="K54" t="n">
         <v>33755</v>
       </c>
-      <c r="H54" t="n">
-        <v>11673</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2739</v>
-      </c>
-      <c r="J54" t="n">
-        <v>8934</v>
+      <c r="L54" t="n">
+        <v>21467</v>
+      </c>
+      <c r="M54" t="n">
+        <v>5156</v>
+      </c>
+      <c r="N54" t="n">
+        <v>16311</v>
       </c>
     </row>
     <row r="55">
@@ -2391,25 +2847,33 @@
         <v>126042</v>
       </c>
       <c r="D55" t="n">
+        <v>44648</v>
+      </c>
+      <c r="E55" t="n">
+        <v>81394</v>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="n">
         <v>19760</v>
       </c>
-      <c r="E55" t="n">
+      <c r="I55" t="n">
         <v>1408.090909090909</v>
       </c>
-      <c r="F55" t="n">
+      <c r="J55" t="n">
         <v>4271</v>
       </c>
-      <c r="G55" t="n">
+      <c r="K55" t="n">
         <v>15489</v>
       </c>
-      <c r="H55" t="n">
-        <v>2916</v>
-      </c>
-      <c r="I55" t="n">
-        <v>595</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2321</v>
+      <c r="L55" t="n">
+        <v>6979</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1667</v>
+      </c>
+      <c r="N55" t="n">
+        <v>5312</v>
       </c>
     </row>
     <row r="56">
@@ -2427,25 +2891,33 @@
         <v>904078</v>
       </c>
       <c r="D56" t="n">
+        <v>546107</v>
+      </c>
+      <c r="E56" t="n">
+        <v>357971</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="n">
         <v>140040</v>
       </c>
-      <c r="E56" t="n">
+      <c r="I56" t="n">
         <v>8187</v>
       </c>
-      <c r="F56" t="n">
+      <c r="J56" t="n">
         <v>49983</v>
       </c>
-      <c r="G56" t="n">
+      <c r="K56" t="n">
         <v>90057</v>
       </c>
-      <c r="H56" t="n">
-        <v>25012</v>
-      </c>
-      <c r="I56" t="n">
-        <v>5225</v>
-      </c>
-      <c r="J56" t="n">
-        <v>19787</v>
+      <c r="L56" t="n">
+        <v>45324</v>
+      </c>
+      <c r="M56" t="n">
+        <v>10165</v>
+      </c>
+      <c r="N56" t="n">
+        <v>35159</v>
       </c>
     </row>
     <row r="57">
@@ -2463,25 +2935,33 @@
         <v>282614</v>
       </c>
       <c r="D57" t="n">
+        <v>144063</v>
+      </c>
+      <c r="E57" t="n">
+        <v>138551</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="n">
         <v>43717</v>
       </c>
-      <c r="E57" t="n">
+      <c r="I57" t="n">
         <v>2079</v>
       </c>
-      <c r="F57" t="n">
+      <c r="J57" t="n">
         <v>20848</v>
       </c>
-      <c r="G57" t="n">
+      <c r="K57" t="n">
         <v>22869</v>
       </c>
-      <c r="H57" t="n">
-        <v>9285</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J57" t="n">
-        <v>7274</v>
+      <c r="L57" t="n">
+        <v>17010</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3607</v>
+      </c>
+      <c r="N57" t="n">
+        <v>13403</v>
       </c>
     </row>
     <row r="58">
@@ -2499,25 +2979,33 @@
         <v>768179</v>
       </c>
       <c r="D58" t="n">
+        <v>452506</v>
+      </c>
+      <c r="E58" t="n">
+        <v>315673</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="n">
         <v>119831</v>
       </c>
-      <c r="E58" t="n">
+      <c r="I58" t="n">
         <v>4627.272727272727</v>
       </c>
-      <c r="F58" t="n">
+      <c r="J58" t="n">
         <v>68931</v>
       </c>
-      <c r="G58" t="n">
+      <c r="K58" t="n">
         <v>50900</v>
       </c>
-      <c r="H58" t="n">
-        <v>23922</v>
-      </c>
-      <c r="I58" t="n">
-        <v>4483</v>
-      </c>
-      <c r="J58" t="n">
-        <v>19439</v>
+      <c r="L58" t="n">
+        <v>52396</v>
+      </c>
+      <c r="M58" t="n">
+        <v>9174</v>
+      </c>
+      <c r="N58" t="n">
+        <v>43222</v>
       </c>
     </row>
     <row r="59">
@@ -2535,25 +3023,33 @@
         <v>566568</v>
       </c>
       <c r="D59" t="n">
+        <v>347852</v>
+      </c>
+      <c r="E59" t="n">
+        <v>218716</v>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="n">
         <v>107374</v>
       </c>
-      <c r="E59" t="n">
+      <c r="I59" t="n">
         <v>5222.272727272727</v>
       </c>
-      <c r="F59" t="n">
+      <c r="J59" t="n">
         <v>49929</v>
       </c>
-      <c r="G59" t="n">
+      <c r="K59" t="n">
         <v>57445</v>
       </c>
-      <c r="H59" t="n">
-        <v>14638</v>
-      </c>
-      <c r="I59" t="n">
-        <v>3627</v>
-      </c>
-      <c r="J59" t="n">
-        <v>11011</v>
+      <c r="L59" t="n">
+        <v>27799</v>
+      </c>
+      <c r="M59" t="n">
+        <v>7132</v>
+      </c>
+      <c r="N59" t="n">
+        <v>20667</v>
       </c>
     </row>
     <row r="60">
@@ -2571,25 +3067,33 @@
         <v>867169</v>
       </c>
       <c r="D60" t="n">
+        <v>550118</v>
+      </c>
+      <c r="E60" t="n">
+        <v>317051</v>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="n">
         <v>148228</v>
       </c>
-      <c r="E60" t="n">
+      <c r="I60" t="n">
         <v>5876.909090909091</v>
       </c>
-      <c r="F60" t="n">
+      <c r="J60" t="n">
         <v>83582</v>
       </c>
-      <c r="G60" t="n">
+      <c r="K60" t="n">
         <v>64646</v>
       </c>
-      <c r="H60" t="n">
-        <v>26792</v>
-      </c>
-      <c r="I60" t="n">
-        <v>6829</v>
-      </c>
-      <c r="J60" t="n">
-        <v>19963</v>
+      <c r="L60" t="n">
+        <v>48520</v>
+      </c>
+      <c r="M60" t="n">
+        <v>12624</v>
+      </c>
+      <c r="N60" t="n">
+        <v>35896</v>
       </c>
     </row>
     <row r="61">
@@ -2607,25 +3111,33 @@
         <v>253468</v>
       </c>
       <c r="D61" t="n">
+        <v>141892</v>
+      </c>
+      <c r="E61" t="n">
+        <v>111576</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
         <v>49078</v>
       </c>
-      <c r="E61" t="n">
+      <c r="I61" t="n">
         <v>2652.363636363636</v>
       </c>
-      <c r="F61" t="n">
+      <c r="J61" t="n">
         <v>19902</v>
       </c>
-      <c r="G61" t="n">
+      <c r="K61" t="n">
         <v>29176</v>
       </c>
-      <c r="H61" t="n">
-        <v>9301</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2229</v>
-      </c>
-      <c r="J61" t="n">
-        <v>7072</v>
+      <c r="L61" t="n">
+        <v>16795</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3967</v>
+      </c>
+      <c r="N61" t="n">
+        <v>12828</v>
       </c>
     </row>
     <row r="62">
@@ -2643,25 +3155,33 @@
         <v>444216</v>
       </c>
       <c r="D62" t="n">
+        <v>273016</v>
+      </c>
+      <c r="E62" t="n">
+        <v>171200</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="n">
         <v>67967</v>
       </c>
-      <c r="E62" t="n">
+      <c r="I62" t="n">
         <v>2280.272727272727</v>
       </c>
-      <c r="F62" t="n">
+      <c r="J62" t="n">
         <v>42884</v>
       </c>
-      <c r="G62" t="n">
+      <c r="K62" t="n">
         <v>25083</v>
       </c>
-      <c r="H62" t="n">
-        <v>17801</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2120</v>
-      </c>
-      <c r="J62" t="n">
-        <v>15681</v>
+      <c r="L62" t="n">
+        <v>31423</v>
+      </c>
+      <c r="M62" t="n">
+        <v>4039</v>
+      </c>
+      <c r="N62" t="n">
+        <v>27384</v>
       </c>
     </row>
     <row r="63">
@@ -2679,25 +3199,33 @@
         <v>234640</v>
       </c>
       <c r="D63" t="n">
+        <v>124133</v>
+      </c>
+      <c r="E63" t="n">
+        <v>110507</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="n">
         <v>38051</v>
       </c>
-      <c r="E63" t="n">
+      <c r="I63" t="n">
         <v>1828.090909090909</v>
       </c>
-      <c r="F63" t="n">
+      <c r="J63" t="n">
         <v>17942</v>
       </c>
-      <c r="G63" t="n">
+      <c r="K63" t="n">
         <v>20109</v>
       </c>
-      <c r="H63" t="n">
-        <v>8215</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1031</v>
-      </c>
-      <c r="J63" t="n">
-        <v>7184</v>
+      <c r="L63" t="n">
+        <v>16687</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2172</v>
+      </c>
+      <c r="N63" t="n">
+        <v>14515</v>
       </c>
     </row>
     <row r="64">
@@ -2715,25 +3243,33 @@
         <v>359823</v>
       </c>
       <c r="D64" t="n">
+        <v>175359</v>
+      </c>
+      <c r="E64" t="n">
+        <v>184464</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="n">
         <v>56266</v>
       </c>
-      <c r="E64" t="n">
+      <c r="I64" t="n">
         <v>3246.272727272727</v>
       </c>
-      <c r="F64" t="n">
+      <c r="J64" t="n">
         <v>20557</v>
       </c>
-      <c r="G64" t="n">
+      <c r="K64" t="n">
         <v>35709</v>
       </c>
-      <c r="H64" t="n">
-        <v>9994</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1445</v>
-      </c>
-      <c r="J64" t="n">
-        <v>8549</v>
+      <c r="L64" t="n">
+        <v>18472</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2941</v>
+      </c>
+      <c r="N64" t="n">
+        <v>15531</v>
       </c>
     </row>
     <row r="65">
@@ -2751,25 +3287,33 @@
         <v>662114</v>
       </c>
       <c r="D65" t="n">
+        <v>371619</v>
+      </c>
+      <c r="E65" t="n">
+        <v>290495</v>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="n">
         <v>114961</v>
       </c>
-      <c r="E65" t="n">
+      <c r="I65" t="n">
         <v>6272.909090909091</v>
       </c>
-      <c r="F65" t="n">
+      <c r="J65" t="n">
         <v>45959</v>
       </c>
-      <c r="G65" t="n">
+      <c r="K65" t="n">
         <v>69002</v>
       </c>
-      <c r="H65" t="n">
-        <v>17459</v>
-      </c>
-      <c r="I65" t="n">
-        <v>3080</v>
-      </c>
-      <c r="J65" t="n">
-        <v>14379</v>
+      <c r="L65" t="n">
+        <v>33195</v>
+      </c>
+      <c r="M65" t="n">
+        <v>5992</v>
+      </c>
+      <c r="N65" t="n">
+        <v>27203</v>
       </c>
     </row>
     <row r="66">
@@ -2787,25 +3331,33 @@
         <v>660311</v>
       </c>
       <c r="D66" t="n">
+        <v>415044</v>
+      </c>
+      <c r="E66" t="n">
+        <v>245267</v>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="n">
         <v>118507</v>
       </c>
-      <c r="E66" t="n">
+      <c r="I66" t="n">
         <v>7772.636363636364</v>
       </c>
-      <c r="F66" t="n">
+      <c r="J66" t="n">
         <v>33008</v>
       </c>
-      <c r="G66" t="n">
+      <c r="K66" t="n">
         <v>85499</v>
       </c>
-      <c r="H66" t="n">
-        <v>20623</v>
-      </c>
-      <c r="I66" t="n">
-        <v>3431</v>
-      </c>
-      <c r="J66" t="n">
-        <v>17192</v>
+      <c r="L66" t="n">
+        <v>35481</v>
+      </c>
+      <c r="M66" t="n">
+        <v>6547</v>
+      </c>
+      <c r="N66" t="n">
+        <v>28934</v>
       </c>
     </row>
     <row r="67">
@@ -2823,25 +3375,33 @@
         <v>425275</v>
       </c>
       <c r="D67" t="n">
+        <v>296284</v>
+      </c>
+      <c r="E67" t="n">
+        <v>128991</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="n">
         <v>70409</v>
       </c>
-      <c r="E67" t="n">
+      <c r="I67" t="n">
         <v>2507.545454545455</v>
       </c>
-      <c r="F67" t="n">
+      <c r="J67" t="n">
         <v>42826</v>
       </c>
-      <c r="G67" t="n">
+      <c r="K67" t="n">
         <v>27583</v>
       </c>
-      <c r="H67" t="n">
-        <v>14109</v>
-      </c>
-      <c r="I67" t="n">
-        <v>3925</v>
-      </c>
-      <c r="J67" t="n">
-        <v>10184</v>
+      <c r="L67" t="n">
+        <v>26935</v>
+      </c>
+      <c r="M67" t="n">
+        <v>7367</v>
+      </c>
+      <c r="N67" t="n">
+        <v>19568</v>
       </c>
     </row>
     <row r="68">
@@ -2859,25 +3419,33 @@
         <v>467936</v>
       </c>
       <c r="D68" t="n">
+        <v>242696</v>
+      </c>
+      <c r="E68" t="n">
+        <v>225240</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="n">
         <v>73266</v>
       </c>
-      <c r="E68" t="n">
+      <c r="I68" t="n">
         <v>3897.181818181818</v>
       </c>
-      <c r="F68" t="n">
+      <c r="J68" t="n">
         <v>30397</v>
       </c>
-      <c r="G68" t="n">
+      <c r="K68" t="n">
         <v>42869</v>
       </c>
-      <c r="H68" t="n">
-        <v>16301</v>
-      </c>
-      <c r="I68" t="n">
-        <v>3053</v>
-      </c>
-      <c r="J68" t="n">
-        <v>13248</v>
+      <c r="L68" t="n">
+        <v>29337</v>
+      </c>
+      <c r="M68" t="n">
+        <v>5624</v>
+      </c>
+      <c r="N68" t="n">
+        <v>23713</v>
       </c>
     </row>
     <row r="69">
@@ -2895,25 +3463,33 @@
         <v>743917</v>
       </c>
       <c r="D69" t="n">
+        <v>466589</v>
+      </c>
+      <c r="E69" t="n">
+        <v>277328</v>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="n">
         <v>122082</v>
       </c>
-      <c r="E69" t="n">
+      <c r="I69" t="n">
         <v>7146.363636363636</v>
       </c>
-      <c r="F69" t="n">
+      <c r="J69" t="n">
         <v>43472</v>
       </c>
-      <c r="G69" t="n">
+      <c r="K69" t="n">
         <v>78610</v>
       </c>
-      <c r="H69" t="n">
-        <v>23147</v>
-      </c>
-      <c r="I69" t="n">
-        <v>2822</v>
-      </c>
-      <c r="J69" t="n">
-        <v>20325</v>
+      <c r="L69" t="n">
+        <v>37394</v>
+      </c>
+      <c r="M69" t="n">
+        <v>5404</v>
+      </c>
+      <c r="N69" t="n">
+        <v>31990</v>
       </c>
     </row>
   </sheetData>

--- a/f_total_cap_nhat.xlsx
+++ b/f_total_cap_nhat.xlsx
@@ -535,13 +535,13 @@
         <v>150469</v>
       </c>
       <c r="L2" t="n">
-        <v>67491</v>
+        <v>77543</v>
       </c>
       <c r="M2" t="n">
-        <v>15230</v>
+        <v>18149</v>
       </c>
       <c r="N2" t="n">
-        <v>52261</v>
+        <v>59394</v>
       </c>
     </row>
     <row r="3">
@@ -579,13 +579,13 @@
         <v>81428</v>
       </c>
       <c r="L3" t="n">
-        <v>108267</v>
+        <v>124018</v>
       </c>
       <c r="M3" t="n">
-        <v>43897</v>
+        <v>51469</v>
       </c>
       <c r="N3" t="n">
-        <v>64370</v>
+        <v>72549</v>
       </c>
     </row>
     <row r="4">
@@ -623,13 +623,13 @@
         <v>18713</v>
       </c>
       <c r="L4" t="n">
-        <v>19849</v>
+        <v>22541</v>
       </c>
       <c r="M4" t="n">
-        <v>3583</v>
+        <v>4275</v>
       </c>
       <c r="N4" t="n">
-        <v>16266</v>
+        <v>18266</v>
       </c>
     </row>
     <row r="5">
@@ -667,13 +667,13 @@
         <v>42408</v>
       </c>
       <c r="L5" t="n">
-        <v>24840</v>
+        <v>28201</v>
       </c>
       <c r="M5" t="n">
-        <v>6742</v>
+        <v>7661</v>
       </c>
       <c r="N5" t="n">
-        <v>18098</v>
+        <v>20540</v>
       </c>
     </row>
     <row r="6">
@@ -711,13 +711,13 @@
         <v>117439</v>
       </c>
       <c r="L6" t="n">
-        <v>71428</v>
+        <v>81432</v>
       </c>
       <c r="M6" t="n">
-        <v>16777</v>
+        <v>19477</v>
       </c>
       <c r="N6" t="n">
-        <v>54651</v>
+        <v>61955</v>
       </c>
     </row>
     <row r="7">
@@ -755,13 +755,13 @@
         <v>19076</v>
       </c>
       <c r="L7" t="n">
-        <v>9944</v>
+        <v>11156</v>
       </c>
       <c r="M7" t="n">
-        <v>1649</v>
+        <v>1914</v>
       </c>
       <c r="N7" t="n">
-        <v>8295</v>
+        <v>9242</v>
       </c>
     </row>
     <row r="8">
@@ -799,13 +799,13 @@
         <v>83014</v>
       </c>
       <c r="L8" t="n">
-        <v>66979</v>
+        <v>76229</v>
       </c>
       <c r="M8" t="n">
-        <v>14900</v>
+        <v>17609</v>
       </c>
       <c r="N8" t="n">
-        <v>52079</v>
+        <v>58620</v>
       </c>
     </row>
     <row r="9">
@@ -843,13 +843,13 @@
         <v>65107</v>
       </c>
       <c r="L9" t="n">
-        <v>50146</v>
+        <v>57115</v>
       </c>
       <c r="M9" t="n">
-        <v>15378</v>
+        <v>18127</v>
       </c>
       <c r="N9" t="n">
-        <v>34768</v>
+        <v>38988</v>
       </c>
     </row>
     <row r="10">
@@ -887,13 +887,13 @@
         <v>151451</v>
       </c>
       <c r="L10" t="n">
-        <v>93311</v>
+        <v>105517</v>
       </c>
       <c r="M10" t="n">
-        <v>31174</v>
+        <v>35942</v>
       </c>
       <c r="N10" t="n">
-        <v>62137</v>
+        <v>69575</v>
       </c>
     </row>
     <row r="11">
@@ -931,13 +931,13 @@
         <v>127517</v>
       </c>
       <c r="L11" t="n">
-        <v>67238</v>
+        <v>77837</v>
       </c>
       <c r="M11" t="n">
-        <v>16442</v>
+        <v>19426</v>
       </c>
       <c r="N11" t="n">
-        <v>50796</v>
+        <v>58411</v>
       </c>
     </row>
     <row r="12">
@@ -975,13 +975,13 @@
         <v>122266</v>
       </c>
       <c r="L12" t="n">
-        <v>80754</v>
+        <v>90980</v>
       </c>
       <c r="M12" t="n">
-        <v>15507</v>
+        <v>18585</v>
       </c>
       <c r="N12" t="n">
-        <v>65247</v>
+        <v>72395</v>
       </c>
     </row>
     <row r="13">
@@ -1019,13 +1019,13 @@
         <v>399425</v>
       </c>
       <c r="L13" t="n">
-        <v>215088</v>
+        <v>251605</v>
       </c>
       <c r="M13" t="n">
-        <v>107015</v>
+        <v>123936</v>
       </c>
       <c r="N13" t="n">
-        <v>108073</v>
+        <v>127669</v>
       </c>
     </row>
     <row r="14">
@@ -1063,13 +1063,13 @@
         <v>274795</v>
       </c>
       <c r="L14" t="n">
-        <v>240276</v>
+        <v>284549</v>
       </c>
       <c r="M14" t="n">
-        <v>115973</v>
+        <v>137420</v>
       </c>
       <c r="N14" t="n">
-        <v>124303</v>
+        <v>147129</v>
       </c>
     </row>
     <row r="15">
@@ -1107,13 +1107,13 @@
         <v>80530</v>
       </c>
       <c r="L15" t="n">
-        <v>75718</v>
+        <v>86966</v>
       </c>
       <c r="M15" t="n">
-        <v>26878</v>
+        <v>31265</v>
       </c>
       <c r="N15" t="n">
-        <v>48840</v>
+        <v>55701</v>
       </c>
     </row>
     <row r="16">
@@ -1151,13 +1151,13 @@
         <v>15975</v>
       </c>
       <c r="L16" t="n">
-        <v>51316</v>
+        <v>56679</v>
       </c>
       <c r="M16" t="n">
-        <v>7910</v>
+        <v>9262</v>
       </c>
       <c r="N16" t="n">
-        <v>43406</v>
+        <v>47417</v>
       </c>
     </row>
     <row r="17">
@@ -1195,13 +1195,13 @@
         <v>26564</v>
       </c>
       <c r="L17" t="n">
-        <v>26726</v>
+        <v>30510</v>
       </c>
       <c r="M17" t="n">
-        <v>7541</v>
+        <v>8858</v>
       </c>
       <c r="N17" t="n">
-        <v>19185</v>
+        <v>21652</v>
       </c>
     </row>
     <row r="18">
@@ -1239,13 +1239,13 @@
         <v>66764</v>
       </c>
       <c r="L18" t="n">
-        <v>70870</v>
+        <v>81004</v>
       </c>
       <c r="M18" t="n">
-        <v>21736</v>
+        <v>25646</v>
       </c>
       <c r="N18" t="n">
-        <v>49134</v>
+        <v>55358</v>
       </c>
     </row>
     <row r="19">
@@ -1283,13 +1283,13 @@
         <v>55231</v>
       </c>
       <c r="L19" t="n">
-        <v>43592</v>
+        <v>49519</v>
       </c>
       <c r="M19" t="n">
-        <v>12626</v>
+        <v>14742</v>
       </c>
       <c r="N19" t="n">
-        <v>30966</v>
+        <v>34777</v>
       </c>
     </row>
     <row r="20">
@@ -1327,13 +1327,13 @@
         <v>58737</v>
       </c>
       <c r="L20" t="n">
-        <v>40208</v>
+        <v>47231</v>
       </c>
       <c r="M20" t="n">
-        <v>10492</v>
+        <v>12557</v>
       </c>
       <c r="N20" t="n">
-        <v>29716</v>
+        <v>34674</v>
       </c>
     </row>
     <row r="21">
@@ -1371,13 +1371,13 @@
         <v>24382</v>
       </c>
       <c r="L21" t="n">
-        <v>15632</v>
+        <v>18358</v>
       </c>
       <c r="M21" t="n">
-        <v>4284</v>
+        <v>5128</v>
       </c>
       <c r="N21" t="n">
-        <v>11348</v>
+        <v>13230</v>
       </c>
     </row>
     <row r="22">
@@ -1415,13 +1415,13 @@
         <v>152229</v>
       </c>
       <c r="L22" t="n">
-        <v>79087</v>
+        <v>91008</v>
       </c>
       <c r="M22" t="n">
-        <v>21671</v>
+        <v>25839</v>
       </c>
       <c r="N22" t="n">
-        <v>57416</v>
+        <v>65169</v>
       </c>
     </row>
     <row r="23">
@@ -1459,13 +1459,13 @@
         <v>40867</v>
       </c>
       <c r="L23" t="n">
-        <v>28778</v>
+        <v>33044</v>
       </c>
       <c r="M23" t="n">
-        <v>6804</v>
+        <v>8117</v>
       </c>
       <c r="N23" t="n">
-        <v>21974</v>
+        <v>24927</v>
       </c>
     </row>
     <row r="24">
@@ -1503,13 +1503,13 @@
         <v>88798</v>
       </c>
       <c r="L24" t="n">
-        <v>94007</v>
+        <v>106760</v>
       </c>
       <c r="M24" t="n">
-        <v>22133</v>
+        <v>26787</v>
       </c>
       <c r="N24" t="n">
-        <v>71874</v>
+        <v>79973</v>
       </c>
     </row>
     <row r="25">
@@ -1547,13 +1547,13 @@
         <v>86600</v>
       </c>
       <c r="L25" t="n">
-        <v>64398</v>
+        <v>74479</v>
       </c>
       <c r="M25" t="n">
-        <v>22189</v>
+        <v>26124</v>
       </c>
       <c r="N25" t="n">
-        <v>42209</v>
+        <v>48355</v>
       </c>
     </row>
     <row r="26">
@@ -1591,13 +1591,13 @@
         <v>95605</v>
       </c>
       <c r="L26" t="n">
-        <v>97934</v>
+        <v>114529</v>
       </c>
       <c r="M26" t="n">
-        <v>32443</v>
+        <v>39114</v>
       </c>
       <c r="N26" t="n">
-        <v>65491</v>
+        <v>75415</v>
       </c>
     </row>
     <row r="27">
@@ -1635,13 +1635,13 @@
         <v>35197</v>
       </c>
       <c r="L27" t="n">
-        <v>35008</v>
+        <v>40234</v>
       </c>
       <c r="M27" t="n">
-        <v>10112</v>
+        <v>11858</v>
       </c>
       <c r="N27" t="n">
-        <v>24896</v>
+        <v>28376</v>
       </c>
     </row>
     <row r="28">
@@ -1679,13 +1679,13 @@
         <v>52800</v>
       </c>
       <c r="L28" t="n">
-        <v>50053</v>
+        <v>56855</v>
       </c>
       <c r="M28" t="n">
-        <v>8481</v>
+        <v>10163</v>
       </c>
       <c r="N28" t="n">
-        <v>41572</v>
+        <v>46692</v>
       </c>
     </row>
     <row r="29">
@@ -1723,13 +1723,13 @@
         <v>34093</v>
       </c>
       <c r="L29" t="n">
-        <v>32058</v>
+        <v>36559</v>
       </c>
       <c r="M29" t="n">
-        <v>5450</v>
+        <v>6482</v>
       </c>
       <c r="N29" t="n">
-        <v>26608</v>
+        <v>30077</v>
       </c>
     </row>
     <row r="30">
@@ -1767,13 +1767,13 @@
         <v>59519</v>
       </c>
       <c r="L30" t="n">
-        <v>30744</v>
+        <v>35366</v>
       </c>
       <c r="M30" t="n">
-        <v>5934</v>
+        <v>7164</v>
       </c>
       <c r="N30" t="n">
-        <v>24810</v>
+        <v>28202</v>
       </c>
     </row>
     <row r="31">
@@ -1811,13 +1811,13 @@
         <v>111215</v>
       </c>
       <c r="L31" t="n">
-        <v>67843</v>
+        <v>77984</v>
       </c>
       <c r="M31" t="n">
-        <v>16543</v>
+        <v>19970</v>
       </c>
       <c r="N31" t="n">
-        <v>51300</v>
+        <v>58014</v>
       </c>
     </row>
     <row r="32">
@@ -1855,13 +1855,13 @@
         <v>135620</v>
       </c>
       <c r="L32" t="n">
-        <v>73512</v>
+        <v>84651</v>
       </c>
       <c r="M32" t="n">
-        <v>18187</v>
+        <v>20965</v>
       </c>
       <c r="N32" t="n">
-        <v>55325</v>
+        <v>63686</v>
       </c>
     </row>
     <row r="33">
@@ -1899,13 +1899,13 @@
         <v>46108</v>
       </c>
       <c r="L33" t="n">
-        <v>48923</v>
+        <v>56833</v>
       </c>
       <c r="M33" t="n">
-        <v>16731</v>
+        <v>19978</v>
       </c>
       <c r="N33" t="n">
-        <v>32192</v>
+        <v>36855</v>
       </c>
     </row>
     <row r="34">
@@ -1943,13 +1943,13 @@
         <v>74035</v>
       </c>
       <c r="L34" t="n">
-        <v>48207</v>
+        <v>56342</v>
       </c>
       <c r="M34" t="n">
-        <v>10666</v>
+        <v>12814</v>
       </c>
       <c r="N34" t="n">
-        <v>37541</v>
+        <v>43528</v>
       </c>
     </row>
     <row r="35">
@@ -1987,13 +1987,13 @@
         <v>134411</v>
       </c>
       <c r="L35" t="n">
-        <v>72687</v>
+        <v>84616</v>
       </c>
       <c r="M35" t="n">
-        <v>14782</v>
+        <v>17861</v>
       </c>
       <c r="N35" t="n">
-        <v>57905</v>
+        <v>66755</v>
       </c>
     </row>
     <row r="36">
@@ -2031,13 +2031,13 @@
         <v>93875</v>
       </c>
       <c r="L36" t="n">
-        <v>54068</v>
+        <v>61912</v>
       </c>
       <c r="M36" t="n">
-        <v>10539</v>
+        <v>12594</v>
       </c>
       <c r="N36" t="n">
-        <v>43529</v>
+        <v>49318</v>
       </c>
     </row>
     <row r="37">
@@ -2075,13 +2075,13 @@
         <v>65690</v>
       </c>
       <c r="L37" t="n">
-        <v>83403</v>
+        <v>95188</v>
       </c>
       <c r="M37" t="n">
-        <v>29599</v>
+        <v>34753</v>
       </c>
       <c r="N37" t="n">
-        <v>53804</v>
+        <v>60435</v>
       </c>
     </row>
     <row r="38">
@@ -2119,13 +2119,13 @@
         <v>7829</v>
       </c>
       <c r="L38" t="n">
-        <v>18338</v>
+        <v>20760</v>
       </c>
       <c r="M38" t="n">
-        <v>3149</v>
+        <v>3769</v>
       </c>
       <c r="N38" t="n">
-        <v>15189</v>
+        <v>16991</v>
       </c>
     </row>
     <row r="39">
@@ -2163,13 +2163,13 @@
         <v>26289</v>
       </c>
       <c r="L39" t="n">
-        <v>19747</v>
+        <v>22353</v>
       </c>
       <c r="M39" t="n">
-        <v>4294</v>
+        <v>4872</v>
       </c>
       <c r="N39" t="n">
-        <v>15453</v>
+        <v>17481</v>
       </c>
     </row>
     <row r="40">
@@ -2207,13 +2207,13 @@
         <v>74072</v>
       </c>
       <c r="L40" t="n">
-        <v>56732</v>
+        <v>64319</v>
       </c>
       <c r="M40" t="n">
-        <v>10482</v>
+        <v>12167</v>
       </c>
       <c r="N40" t="n">
-        <v>46250</v>
+        <v>52152</v>
       </c>
     </row>
     <row r="41">
@@ -2251,13 +2251,13 @@
         <v>11564</v>
       </c>
       <c r="L41" t="n">
-        <v>8335</v>
+        <v>9346</v>
       </c>
       <c r="M41" t="n">
-        <v>1275</v>
+        <v>1495</v>
       </c>
       <c r="N41" t="n">
-        <v>7060</v>
+        <v>7851</v>
       </c>
     </row>
     <row r="42">
@@ -2295,13 +2295,13 @@
         <v>41594</v>
       </c>
       <c r="L42" t="n">
-        <v>59151</v>
+        <v>67141</v>
       </c>
       <c r="M42" t="n">
-        <v>12148</v>
+        <v>14382</v>
       </c>
       <c r="N42" t="n">
-        <v>47003</v>
+        <v>52759</v>
       </c>
     </row>
     <row r="43">
@@ -2339,13 +2339,13 @@
         <v>39097</v>
       </c>
       <c r="L43" t="n">
-        <v>41035</v>
+        <v>46365</v>
       </c>
       <c r="M43" t="n">
-        <v>9938</v>
+        <v>11715</v>
       </c>
       <c r="N43" t="n">
-        <v>31097</v>
+        <v>34650</v>
       </c>
     </row>
     <row r="44">
@@ -2383,13 +2383,13 @@
         <v>90813</v>
       </c>
       <c r="L44" t="n">
-        <v>75972</v>
+        <v>85429</v>
       </c>
       <c r="M44" t="n">
-        <v>21474</v>
+        <v>24755</v>
       </c>
       <c r="N44" t="n">
-        <v>54498</v>
+        <v>60674</v>
       </c>
     </row>
     <row r="45">
@@ -2427,13 +2427,13 @@
         <v>74362</v>
       </c>
       <c r="L45" t="n">
-        <v>55239</v>
+        <v>63736</v>
       </c>
       <c r="M45" t="n">
-        <v>11765</v>
+        <v>13916</v>
       </c>
       <c r="N45" t="n">
-        <v>43474</v>
+        <v>49820</v>
       </c>
     </row>
     <row r="46">
@@ -2471,13 +2471,13 @@
         <v>66503</v>
       </c>
       <c r="L46" t="n">
-        <v>70781</v>
+        <v>79330</v>
       </c>
       <c r="M46" t="n">
-        <v>12157</v>
+        <v>14552</v>
       </c>
       <c r="N46" t="n">
-        <v>58624</v>
+        <v>64778</v>
       </c>
     </row>
     <row r="47">
@@ -2515,13 +2515,13 @@
         <v>286539</v>
       </c>
       <c r="L47" t="n">
-        <v>140410</v>
+        <v>164506</v>
       </c>
       <c r="M47" t="n">
-        <v>58595</v>
+        <v>68203</v>
       </c>
       <c r="N47" t="n">
-        <v>81815</v>
+        <v>96303</v>
       </c>
     </row>
     <row r="48">
@@ -2559,13 +2559,13 @@
         <v>262442</v>
       </c>
       <c r="L48" t="n">
-        <v>140729</v>
+        <v>166717</v>
       </c>
       <c r="M48" t="n">
-        <v>58059</v>
+        <v>69018</v>
       </c>
       <c r="N48" t="n">
-        <v>82670</v>
+        <v>97699</v>
       </c>
     </row>
     <row r="49">
@@ -2603,13 +2603,13 @@
         <v>73813</v>
       </c>
       <c r="L49" t="n">
-        <v>52505</v>
+        <v>60090</v>
       </c>
       <c r="M49" t="n">
-        <v>15890</v>
+        <v>18453</v>
       </c>
       <c r="N49" t="n">
-        <v>36615</v>
+        <v>41637</v>
       </c>
     </row>
     <row r="50">
@@ -2647,13 +2647,13 @@
         <v>14115</v>
       </c>
       <c r="L50" t="n">
-        <v>43502</v>
+        <v>47880</v>
       </c>
       <c r="M50" t="n">
-        <v>5745</v>
+        <v>6725</v>
       </c>
       <c r="N50" t="n">
-        <v>37757</v>
+        <v>41155</v>
       </c>
     </row>
     <row r="51">
@@ -2691,13 +2691,13 @@
         <v>14887</v>
       </c>
       <c r="L51" t="n">
-        <v>21744</v>
+        <v>24717</v>
       </c>
       <c r="M51" t="n">
-        <v>4996</v>
+        <v>5869</v>
       </c>
       <c r="N51" t="n">
-        <v>16748</v>
+        <v>18848</v>
       </c>
     </row>
     <row r="52">
@@ -2735,13 +2735,13 @@
         <v>52222</v>
       </c>
       <c r="L52" t="n">
-        <v>52384</v>
+        <v>59453</v>
       </c>
       <c r="M52" t="n">
-        <v>13576</v>
+        <v>15999</v>
       </c>
       <c r="N52" t="n">
-        <v>38808</v>
+        <v>43454</v>
       </c>
     </row>
     <row r="53">
@@ -2779,13 +2779,13 @@
         <v>29739</v>
       </c>
       <c r="L53" t="n">
-        <v>37819</v>
+        <v>42753</v>
       </c>
       <c r="M53" t="n">
-        <v>9752</v>
+        <v>11352</v>
       </c>
       <c r="N53" t="n">
-        <v>28067</v>
+        <v>31401</v>
       </c>
     </row>
     <row r="54">
@@ -2823,13 +2823,13 @@
         <v>33755</v>
       </c>
       <c r="L54" t="n">
-        <v>34891</v>
+        <v>40966</v>
       </c>
       <c r="M54" t="n">
-        <v>8727</v>
+        <v>10466</v>
       </c>
       <c r="N54" t="n">
-        <v>26164</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="55">
@@ -2867,13 +2867,13 @@
         <v>15489</v>
       </c>
       <c r="L55" t="n">
-        <v>12978</v>
+        <v>15269</v>
       </c>
       <c r="M55" t="n">
-        <v>3418</v>
+        <v>4121</v>
       </c>
       <c r="N55" t="n">
-        <v>9560</v>
+        <v>11148</v>
       </c>
     </row>
     <row r="56">
@@ -2911,13 +2911,13 @@
         <v>90057</v>
       </c>
       <c r="L56" t="n">
-        <v>69044</v>
+        <v>79079</v>
       </c>
       <c r="M56" t="n">
-        <v>17163</v>
+        <v>20458</v>
       </c>
       <c r="N56" t="n">
-        <v>51881</v>
+        <v>58621</v>
       </c>
     </row>
     <row r="57">
@@ -2955,13 +2955,13 @@
         <v>22869</v>
       </c>
       <c r="L57" t="n">
-        <v>25340</v>
+        <v>28987</v>
       </c>
       <c r="M57" t="n">
-        <v>5688</v>
+        <v>6771</v>
       </c>
       <c r="N57" t="n">
-        <v>19652</v>
+        <v>22216</v>
       </c>
     </row>
     <row r="58">
@@ -2999,13 +2999,13 @@
         <v>50900</v>
       </c>
       <c r="L58" t="n">
-        <v>79658</v>
+        <v>90027</v>
       </c>
       <c r="M58" t="n">
-        <v>16252</v>
+        <v>19654</v>
       </c>
       <c r="N58" t="n">
-        <v>63406</v>
+        <v>70373</v>
       </c>
     </row>
     <row r="59">
@@ -3043,13 +3043,13 @@
         <v>57445</v>
       </c>
       <c r="L59" t="n">
-        <v>46292</v>
+        <v>53354</v>
       </c>
       <c r="M59" t="n">
-        <v>13229</v>
+        <v>15640</v>
       </c>
       <c r="N59" t="n">
-        <v>33063</v>
+        <v>37714</v>
       </c>
     </row>
     <row r="60">
@@ -3087,13 +3087,13 @@
         <v>64646</v>
       </c>
       <c r="L60" t="n">
-        <v>78332</v>
+        <v>91484</v>
       </c>
       <c r="M60" t="n">
-        <v>23220</v>
+        <v>28129</v>
       </c>
       <c r="N60" t="n">
-        <v>55112</v>
+        <v>63355</v>
       </c>
     </row>
     <row r="61">
@@ -3131,13 +3131,13 @@
         <v>29176</v>
       </c>
       <c r="L61" t="n">
-        <v>26506</v>
+        <v>30369</v>
       </c>
       <c r="M61" t="n">
-        <v>6683</v>
+        <v>7828</v>
       </c>
       <c r="N61" t="n">
-        <v>19823</v>
+        <v>22541</v>
       </c>
     </row>
     <row r="62">
@@ -3175,13 +3175,13 @@
         <v>25083</v>
       </c>
       <c r="L62" t="n">
-        <v>45221</v>
+        <v>51137</v>
       </c>
       <c r="M62" t="n">
-        <v>6672</v>
+        <v>8000</v>
       </c>
       <c r="N62" t="n">
-        <v>38549</v>
+        <v>43137</v>
       </c>
     </row>
     <row r="63">
@@ -3219,13 +3219,13 @@
         <v>20109</v>
       </c>
       <c r="L63" t="n">
-        <v>26589</v>
+        <v>30214</v>
       </c>
       <c r="M63" t="n">
-        <v>3864</v>
+        <v>4616</v>
       </c>
       <c r="N63" t="n">
-        <v>22725</v>
+        <v>25598</v>
       </c>
     </row>
     <row r="64">
@@ -3263,13 +3263,13 @@
         <v>35709</v>
       </c>
       <c r="L64" t="n">
-        <v>26935</v>
+        <v>30821</v>
       </c>
       <c r="M64" t="n">
-        <v>4922</v>
+        <v>5930</v>
       </c>
       <c r="N64" t="n">
-        <v>22013</v>
+        <v>24891</v>
       </c>
     </row>
     <row r="65">
@@ -3307,13 +3307,13 @@
         <v>69002</v>
       </c>
       <c r="L65" t="n">
-        <v>54447</v>
+        <v>62227</v>
       </c>
       <c r="M65" t="n">
-        <v>11380</v>
+        <v>13788</v>
       </c>
       <c r="N65" t="n">
-        <v>43067</v>
+        <v>48439</v>
       </c>
     </row>
     <row r="66">
@@ -3351,13 +3351,13 @@
         <v>85499</v>
       </c>
       <c r="L66" t="n">
-        <v>57565</v>
+        <v>66080</v>
       </c>
       <c r="M66" t="n">
-        <v>11579</v>
+        <v>13351</v>
       </c>
       <c r="N66" t="n">
-        <v>45986</v>
+        <v>52729</v>
       </c>
     </row>
     <row r="67">
@@ -3395,13 +3395,13 @@
         <v>27583</v>
       </c>
       <c r="L67" t="n">
-        <v>41532</v>
+        <v>48097</v>
       </c>
       <c r="M67" t="n">
-        <v>12760</v>
+        <v>15272</v>
       </c>
       <c r="N67" t="n">
-        <v>28772</v>
+        <v>32825</v>
       </c>
     </row>
     <row r="68">
@@ -3439,13 +3439,13 @@
         <v>42869</v>
       </c>
       <c r="L68" t="n">
-        <v>42400</v>
+        <v>49330</v>
       </c>
       <c r="M68" t="n">
-        <v>9064</v>
+        <v>10894</v>
       </c>
       <c r="N68" t="n">
-        <v>33336</v>
+        <v>38436</v>
       </c>
     </row>
     <row r="69">
@@ -3483,13 +3483,13 @@
         <v>78610</v>
       </c>
       <c r="L69" t="n">
-        <v>60845</v>
+        <v>70515</v>
       </c>
       <c r="M69" t="n">
-        <v>10127</v>
+        <v>12319</v>
       </c>
       <c r="N69" t="n">
-        <v>50718</v>
+        <v>58196</v>
       </c>
     </row>
   </sheetData>

--- a/f_total_cap_nhat.xlsx
+++ b/f_total_cap_nhat.xlsx
@@ -535,13 +535,13 @@
         <v>150469</v>
       </c>
       <c r="L2" t="n">
-        <v>77543</v>
+        <v>85966</v>
       </c>
       <c r="M2" t="n">
-        <v>18149</v>
+        <v>21659</v>
       </c>
       <c r="N2" t="n">
-        <v>59394</v>
+        <v>64307</v>
       </c>
     </row>
     <row r="3">
@@ -579,13 +579,13 @@
         <v>81428</v>
       </c>
       <c r="L3" t="n">
-        <v>124018</v>
+        <v>140160</v>
       </c>
       <c r="M3" t="n">
-        <v>51469</v>
+        <v>60665</v>
       </c>
       <c r="N3" t="n">
-        <v>72549</v>
+        <v>79495</v>
       </c>
     </row>
     <row r="4">
@@ -623,13 +623,13 @@
         <v>18713</v>
       </c>
       <c r="L4" t="n">
-        <v>22541</v>
+        <v>24160</v>
       </c>
       <c r="M4" t="n">
-        <v>4275</v>
+        <v>4940</v>
       </c>
       <c r="N4" t="n">
-        <v>18266</v>
+        <v>19220</v>
       </c>
     </row>
     <row r="5">
@@ -667,13 +667,13 @@
         <v>42408</v>
       </c>
       <c r="L5" t="n">
-        <v>28201</v>
+        <v>30808</v>
       </c>
       <c r="M5" t="n">
-        <v>7661</v>
+        <v>8728</v>
       </c>
       <c r="N5" t="n">
-        <v>20540</v>
+        <v>22080</v>
       </c>
     </row>
     <row r="6">
@@ -711,13 +711,13 @@
         <v>117439</v>
       </c>
       <c r="L6" t="n">
-        <v>81432</v>
+        <v>89042</v>
       </c>
       <c r="M6" t="n">
-        <v>19477</v>
+        <v>22326</v>
       </c>
       <c r="N6" t="n">
-        <v>61955</v>
+        <v>66716</v>
       </c>
     </row>
     <row r="7">
@@ -755,13 +755,13 @@
         <v>19076</v>
       </c>
       <c r="L7" t="n">
-        <v>11156</v>
+        <v>12519</v>
       </c>
       <c r="M7" t="n">
-        <v>1914</v>
+        <v>2290</v>
       </c>
       <c r="N7" t="n">
-        <v>9242</v>
+        <v>10229</v>
       </c>
     </row>
     <row r="8">
@@ -799,13 +799,13 @@
         <v>83014</v>
       </c>
       <c r="L8" t="n">
-        <v>76229</v>
+        <v>83803</v>
       </c>
       <c r="M8" t="n">
-        <v>17609</v>
+        <v>20864</v>
       </c>
       <c r="N8" t="n">
-        <v>58620</v>
+        <v>62939</v>
       </c>
     </row>
     <row r="9">
@@ -843,13 +843,13 @@
         <v>65107</v>
       </c>
       <c r="L9" t="n">
-        <v>57115</v>
+        <v>62936</v>
       </c>
       <c r="M9" t="n">
-        <v>18127</v>
+        <v>20983</v>
       </c>
       <c r="N9" t="n">
-        <v>38988</v>
+        <v>41953</v>
       </c>
     </row>
     <row r="10">
@@ -887,13 +887,13 @@
         <v>151451</v>
       </c>
       <c r="L10" t="n">
-        <v>105517</v>
+        <v>115876</v>
       </c>
       <c r="M10" t="n">
-        <v>35942</v>
+        <v>41671</v>
       </c>
       <c r="N10" t="n">
-        <v>69575</v>
+        <v>74205</v>
       </c>
     </row>
     <row r="11">
@@ -931,13 +931,13 @@
         <v>127517</v>
       </c>
       <c r="L11" t="n">
-        <v>77837</v>
+        <v>86860</v>
       </c>
       <c r="M11" t="n">
-        <v>19426</v>
+        <v>23185</v>
       </c>
       <c r="N11" t="n">
-        <v>58411</v>
+        <v>63675</v>
       </c>
     </row>
     <row r="12">
@@ -975,13 +975,13 @@
         <v>122266</v>
       </c>
       <c r="L12" t="n">
-        <v>90980</v>
+        <v>100972</v>
       </c>
       <c r="M12" t="n">
-        <v>18585</v>
+        <v>22552</v>
       </c>
       <c r="N12" t="n">
-        <v>72395</v>
+        <v>78420</v>
       </c>
     </row>
     <row r="13">
@@ -1019,13 +1019,13 @@
         <v>399425</v>
       </c>
       <c r="L13" t="n">
-        <v>251605</v>
+        <v>278129</v>
       </c>
       <c r="M13" t="n">
-        <v>123936</v>
+        <v>140691</v>
       </c>
       <c r="N13" t="n">
-        <v>127669</v>
+        <v>137438</v>
       </c>
     </row>
     <row r="14">
@@ -1063,13 +1063,13 @@
         <v>274795</v>
       </c>
       <c r="L14" t="n">
-        <v>284549</v>
+        <v>320675</v>
       </c>
       <c r="M14" t="n">
-        <v>137420</v>
+        <v>159854</v>
       </c>
       <c r="N14" t="n">
-        <v>147129</v>
+        <v>160821</v>
       </c>
     </row>
     <row r="15">
@@ -1107,13 +1107,13 @@
         <v>80530</v>
       </c>
       <c r="L15" t="n">
-        <v>86966</v>
+        <v>99160</v>
       </c>
       <c r="M15" t="n">
-        <v>31265</v>
+        <v>37259</v>
       </c>
       <c r="N15" t="n">
-        <v>55701</v>
+        <v>61901</v>
       </c>
     </row>
     <row r="16">
@@ -1151,13 +1151,13 @@
         <v>15975</v>
       </c>
       <c r="L16" t="n">
-        <v>56679</v>
+        <v>63067</v>
       </c>
       <c r="M16" t="n">
-        <v>9262</v>
+        <v>10966</v>
       </c>
       <c r="N16" t="n">
-        <v>47417</v>
+        <v>52101</v>
       </c>
     </row>
     <row r="17">
@@ -1195,13 +1195,13 @@
         <v>26564</v>
       </c>
       <c r="L17" t="n">
-        <v>30510</v>
+        <v>33399</v>
       </c>
       <c r="M17" t="n">
-        <v>8858</v>
+        <v>10302</v>
       </c>
       <c r="N17" t="n">
-        <v>21652</v>
+        <v>23097</v>
       </c>
     </row>
     <row r="18">
@@ -1239,13 +1239,13 @@
         <v>66764</v>
       </c>
       <c r="L18" t="n">
-        <v>81004</v>
+        <v>92263</v>
       </c>
       <c r="M18" t="n">
-        <v>25646</v>
+        <v>30719</v>
       </c>
       <c r="N18" t="n">
-        <v>55358</v>
+        <v>61544</v>
       </c>
     </row>
     <row r="19">
@@ -1283,13 +1283,13 @@
         <v>55231</v>
       </c>
       <c r="L19" t="n">
-        <v>49519</v>
+        <v>54396</v>
       </c>
       <c r="M19" t="n">
-        <v>14742</v>
+        <v>17126</v>
       </c>
       <c r="N19" t="n">
-        <v>34777</v>
+        <v>37270</v>
       </c>
     </row>
     <row r="20">
@@ -1327,13 +1327,13 @@
         <v>58737</v>
       </c>
       <c r="L20" t="n">
-        <v>47231</v>
+        <v>53877</v>
       </c>
       <c r="M20" t="n">
-        <v>12557</v>
+        <v>15291</v>
       </c>
       <c r="N20" t="n">
-        <v>34674</v>
+        <v>38586</v>
       </c>
     </row>
     <row r="21">
@@ -1371,13 +1371,13 @@
         <v>24382</v>
       </c>
       <c r="L21" t="n">
-        <v>18358</v>
+        <v>20689</v>
       </c>
       <c r="M21" t="n">
-        <v>5128</v>
+        <v>5894</v>
       </c>
       <c r="N21" t="n">
-        <v>13230</v>
+        <v>14795</v>
       </c>
     </row>
     <row r="22">
@@ -1415,13 +1415,13 @@
         <v>152229</v>
       </c>
       <c r="L22" t="n">
-        <v>91008</v>
+        <v>101195</v>
       </c>
       <c r="M22" t="n">
-        <v>25839</v>
+        <v>31048</v>
       </c>
       <c r="N22" t="n">
-        <v>65169</v>
+        <v>70147</v>
       </c>
     </row>
     <row r="23">
@@ -1459,13 +1459,13 @@
         <v>40867</v>
       </c>
       <c r="L23" t="n">
-        <v>33044</v>
+        <v>37369</v>
       </c>
       <c r="M23" t="n">
-        <v>8117</v>
+        <v>9886</v>
       </c>
       <c r="N23" t="n">
-        <v>24927</v>
+        <v>27483</v>
       </c>
     </row>
     <row r="24">
@@ -1503,13 +1503,13 @@
         <v>88798</v>
       </c>
       <c r="L24" t="n">
-        <v>106760</v>
+        <v>121362</v>
       </c>
       <c r="M24" t="n">
-        <v>26787</v>
+        <v>32879</v>
       </c>
       <c r="N24" t="n">
-        <v>79973</v>
+        <v>88483</v>
       </c>
     </row>
     <row r="25">
@@ -1547,13 +1547,13 @@
         <v>86600</v>
       </c>
       <c r="L25" t="n">
-        <v>74479</v>
+        <v>85819</v>
       </c>
       <c r="M25" t="n">
-        <v>26124</v>
+        <v>31958</v>
       </c>
       <c r="N25" t="n">
-        <v>48355</v>
+        <v>53861</v>
       </c>
     </row>
     <row r="26">
@@ -1591,13 +1591,13 @@
         <v>95605</v>
       </c>
       <c r="L26" t="n">
-        <v>114529</v>
+        <v>134161</v>
       </c>
       <c r="M26" t="n">
-        <v>39114</v>
+        <v>48677</v>
       </c>
       <c r="N26" t="n">
-        <v>75415</v>
+        <v>85484</v>
       </c>
     </row>
     <row r="27">
@@ -1635,13 +1635,13 @@
         <v>35197</v>
       </c>
       <c r="L27" t="n">
-        <v>40234</v>
+        <v>44329</v>
       </c>
       <c r="M27" t="n">
-        <v>11858</v>
+        <v>13756</v>
       </c>
       <c r="N27" t="n">
-        <v>28376</v>
+        <v>30573</v>
       </c>
     </row>
     <row r="28">
@@ -1679,13 +1679,13 @@
         <v>52800</v>
       </c>
       <c r="L28" t="n">
-        <v>56855</v>
+        <v>62106</v>
       </c>
       <c r="M28" t="n">
-        <v>10163</v>
+        <v>12058</v>
       </c>
       <c r="N28" t="n">
-        <v>46692</v>
+        <v>50048</v>
       </c>
     </row>
     <row r="29">
@@ -1723,13 +1723,13 @@
         <v>34093</v>
       </c>
       <c r="L29" t="n">
-        <v>36559</v>
+        <v>40551</v>
       </c>
       <c r="M29" t="n">
-        <v>6482</v>
+        <v>7705</v>
       </c>
       <c r="N29" t="n">
-        <v>30077</v>
+        <v>32846</v>
       </c>
     </row>
     <row r="30">
@@ -1767,13 +1767,13 @@
         <v>59519</v>
       </c>
       <c r="L30" t="n">
-        <v>35366</v>
+        <v>40087</v>
       </c>
       <c r="M30" t="n">
-        <v>7164</v>
+        <v>9103</v>
       </c>
       <c r="N30" t="n">
-        <v>28202</v>
+        <v>30984</v>
       </c>
     </row>
     <row r="31">
@@ -1811,13 +1811,13 @@
         <v>111215</v>
       </c>
       <c r="L31" t="n">
-        <v>77984</v>
+        <v>88709</v>
       </c>
       <c r="M31" t="n">
-        <v>19970</v>
+        <v>24678</v>
       </c>
       <c r="N31" t="n">
-        <v>58014</v>
+        <v>64031</v>
       </c>
     </row>
     <row r="32">
@@ -1855,13 +1855,13 @@
         <v>135620</v>
       </c>
       <c r="L32" t="n">
-        <v>84651</v>
+        <v>93200</v>
       </c>
       <c r="M32" t="n">
-        <v>20965</v>
+        <v>24512</v>
       </c>
       <c r="N32" t="n">
-        <v>63686</v>
+        <v>68688</v>
       </c>
     </row>
     <row r="33">
@@ -1899,13 +1899,13 @@
         <v>46108</v>
       </c>
       <c r="L33" t="n">
-        <v>56833</v>
+        <v>64341</v>
       </c>
       <c r="M33" t="n">
-        <v>19978</v>
+        <v>24063</v>
       </c>
       <c r="N33" t="n">
-        <v>36855</v>
+        <v>40278</v>
       </c>
     </row>
     <row r="34">
@@ -1943,13 +1943,13 @@
         <v>74035</v>
       </c>
       <c r="L34" t="n">
-        <v>56342</v>
+        <v>64598</v>
       </c>
       <c r="M34" t="n">
-        <v>12814</v>
+        <v>15594</v>
       </c>
       <c r="N34" t="n">
-        <v>43528</v>
+        <v>49004</v>
       </c>
     </row>
     <row r="35">
@@ -1987,13 +1987,13 @@
         <v>134411</v>
       </c>
       <c r="L35" t="n">
-        <v>84616</v>
+        <v>94162</v>
       </c>
       <c r="M35" t="n">
-        <v>17861</v>
+        <v>21343</v>
       </c>
       <c r="N35" t="n">
-        <v>66755</v>
+        <v>72819</v>
       </c>
     </row>
     <row r="36">
@@ -2031,13 +2031,13 @@
         <v>93875</v>
       </c>
       <c r="L36" t="n">
-        <v>61912</v>
+        <v>68260</v>
       </c>
       <c r="M36" t="n">
-        <v>12594</v>
+        <v>15050</v>
       </c>
       <c r="N36" t="n">
-        <v>49318</v>
+        <v>53210</v>
       </c>
     </row>
     <row r="37">
@@ -2075,13 +2075,13 @@
         <v>65690</v>
       </c>
       <c r="L37" t="n">
-        <v>95188</v>
+        <v>107273</v>
       </c>
       <c r="M37" t="n">
-        <v>34753</v>
+        <v>41243</v>
       </c>
       <c r="N37" t="n">
-        <v>60435</v>
+        <v>66030</v>
       </c>
     </row>
     <row r="38">
@@ -2119,13 +2119,13 @@
         <v>7829</v>
       </c>
       <c r="L38" t="n">
-        <v>20760</v>
+        <v>22203</v>
       </c>
       <c r="M38" t="n">
-        <v>3769</v>
+        <v>4353</v>
       </c>
       <c r="N38" t="n">
-        <v>16991</v>
+        <v>17850</v>
       </c>
     </row>
     <row r="39">
@@ -2163,13 +2163,13 @@
         <v>26289</v>
       </c>
       <c r="L39" t="n">
-        <v>22353</v>
+        <v>24301</v>
       </c>
       <c r="M39" t="n">
-        <v>4872</v>
+        <v>5557</v>
       </c>
       <c r="N39" t="n">
-        <v>17481</v>
+        <v>18744</v>
       </c>
     </row>
     <row r="40">
@@ -2207,13 +2207,13 @@
         <v>74072</v>
       </c>
       <c r="L40" t="n">
-        <v>64319</v>
+        <v>69865</v>
       </c>
       <c r="M40" t="n">
-        <v>12167</v>
+        <v>13942</v>
       </c>
       <c r="N40" t="n">
-        <v>52152</v>
+        <v>55923</v>
       </c>
     </row>
     <row r="41">
@@ -2251,13 +2251,13 @@
         <v>11564</v>
       </c>
       <c r="L41" t="n">
-        <v>9346</v>
+        <v>10453</v>
       </c>
       <c r="M41" t="n">
-        <v>1495</v>
+        <v>1804</v>
       </c>
       <c r="N41" t="n">
-        <v>7851</v>
+        <v>8649</v>
       </c>
     </row>
     <row r="42">
@@ -2295,13 +2295,13 @@
         <v>41594</v>
       </c>
       <c r="L42" t="n">
-        <v>67141</v>
+        <v>73521</v>
       </c>
       <c r="M42" t="n">
-        <v>14382</v>
+        <v>17064</v>
       </c>
       <c r="N42" t="n">
-        <v>52759</v>
+        <v>56457</v>
       </c>
     </row>
     <row r="43">
@@ -2339,13 +2339,13 @@
         <v>39097</v>
       </c>
       <c r="L43" t="n">
-        <v>46365</v>
+        <v>50819</v>
       </c>
       <c r="M43" t="n">
-        <v>11715</v>
+        <v>13659</v>
       </c>
       <c r="N43" t="n">
-        <v>34650</v>
+        <v>37160</v>
       </c>
     </row>
     <row r="44">
@@ -2383,13 +2383,13 @@
         <v>90813</v>
       </c>
       <c r="L44" t="n">
-        <v>85429</v>
+        <v>93302</v>
       </c>
       <c r="M44" t="n">
-        <v>24755</v>
+        <v>28804</v>
       </c>
       <c r="N44" t="n">
-        <v>60674</v>
+        <v>64498</v>
       </c>
     </row>
     <row r="45">
@@ -2427,13 +2427,13 @@
         <v>74362</v>
       </c>
       <c r="L45" t="n">
-        <v>63736</v>
+        <v>70818</v>
       </c>
       <c r="M45" t="n">
-        <v>13916</v>
+        <v>16680</v>
       </c>
       <c r="N45" t="n">
-        <v>49820</v>
+        <v>54138</v>
       </c>
     </row>
     <row r="46">
@@ -2471,13 +2471,13 @@
         <v>66503</v>
       </c>
       <c r="L46" t="n">
-        <v>79330</v>
+        <v>87642</v>
       </c>
       <c r="M46" t="n">
-        <v>14552</v>
+        <v>17682</v>
       </c>
       <c r="N46" t="n">
-        <v>64778</v>
+        <v>69960</v>
       </c>
     </row>
     <row r="47">
@@ -2515,13 +2515,13 @@
         <v>286539</v>
       </c>
       <c r="L47" t="n">
-        <v>164506</v>
+        <v>181434</v>
       </c>
       <c r="M47" t="n">
-        <v>68203</v>
+        <v>77966</v>
       </c>
       <c r="N47" t="n">
-        <v>96303</v>
+        <v>103468</v>
       </c>
     </row>
     <row r="48">
@@ -2559,13 +2559,13 @@
         <v>262442</v>
       </c>
       <c r="L48" t="n">
-        <v>166717</v>
+        <v>187520</v>
       </c>
       <c r="M48" t="n">
-        <v>69018</v>
+        <v>80961</v>
       </c>
       <c r="N48" t="n">
-        <v>97699</v>
+        <v>106559</v>
       </c>
     </row>
     <row r="49">
@@ -2603,13 +2603,13 @@
         <v>73813</v>
       </c>
       <c r="L49" t="n">
-        <v>60090</v>
+        <v>67923</v>
       </c>
       <c r="M49" t="n">
-        <v>18453</v>
+        <v>21973</v>
       </c>
       <c r="N49" t="n">
-        <v>41637</v>
+        <v>45950</v>
       </c>
     </row>
     <row r="50">
@@ -2647,13 +2647,13 @@
         <v>14115</v>
       </c>
       <c r="L50" t="n">
-        <v>47880</v>
+        <v>53082</v>
       </c>
       <c r="M50" t="n">
-        <v>6725</v>
+        <v>7998</v>
       </c>
       <c r="N50" t="n">
-        <v>41155</v>
+        <v>45084</v>
       </c>
     </row>
     <row r="51">
@@ -2691,13 +2691,13 @@
         <v>14887</v>
       </c>
       <c r="L51" t="n">
-        <v>24717</v>
+        <v>26848</v>
       </c>
       <c r="M51" t="n">
-        <v>5869</v>
+        <v>6817</v>
       </c>
       <c r="N51" t="n">
-        <v>18848</v>
+        <v>20031</v>
       </c>
     </row>
     <row r="52">
@@ -2735,13 +2735,13 @@
         <v>52222</v>
       </c>
       <c r="L52" t="n">
-        <v>59453</v>
+        <v>67178</v>
       </c>
       <c r="M52" t="n">
-        <v>15999</v>
+        <v>19284</v>
       </c>
       <c r="N52" t="n">
-        <v>43454</v>
+        <v>47894</v>
       </c>
     </row>
     <row r="53">
@@ -2779,13 +2779,13 @@
         <v>29739</v>
       </c>
       <c r="L53" t="n">
-        <v>42753</v>
+        <v>46715</v>
       </c>
       <c r="M53" t="n">
-        <v>11352</v>
+        <v>13156</v>
       </c>
       <c r="N53" t="n">
-        <v>31401</v>
+        <v>33559</v>
       </c>
     </row>
     <row r="54">
@@ -2823,13 +2823,13 @@
         <v>33755</v>
       </c>
       <c r="L54" t="n">
-        <v>40966</v>
+        <v>46525</v>
       </c>
       <c r="M54" t="n">
-        <v>10466</v>
+        <v>12763</v>
       </c>
       <c r="N54" t="n">
-        <v>30500</v>
+        <v>33762</v>
       </c>
     </row>
     <row r="55">
@@ -2867,13 +2867,13 @@
         <v>15489</v>
       </c>
       <c r="L55" t="n">
-        <v>15269</v>
+        <v>17206</v>
       </c>
       <c r="M55" t="n">
-        <v>4121</v>
+        <v>4753</v>
       </c>
       <c r="N55" t="n">
-        <v>11148</v>
+        <v>12453</v>
       </c>
     </row>
     <row r="56">
@@ -2911,13 +2911,13 @@
         <v>90057</v>
       </c>
       <c r="L56" t="n">
-        <v>79079</v>
+        <v>87572</v>
       </c>
       <c r="M56" t="n">
-        <v>20458</v>
+        <v>24692</v>
       </c>
       <c r="N56" t="n">
-        <v>58621</v>
+        <v>62880</v>
       </c>
     </row>
     <row r="57">
@@ -2955,13 +2955,13 @@
         <v>22869</v>
       </c>
       <c r="L57" t="n">
-        <v>28987</v>
+        <v>32674</v>
       </c>
       <c r="M57" t="n">
-        <v>6771</v>
+        <v>8272</v>
       </c>
       <c r="N57" t="n">
-        <v>22216</v>
+        <v>24402</v>
       </c>
     </row>
     <row r="58">
@@ -2999,13 +2999,13 @@
         <v>50900</v>
       </c>
       <c r="L58" t="n">
-        <v>90027</v>
+        <v>101727</v>
       </c>
       <c r="M58" t="n">
-        <v>19654</v>
+        <v>24233</v>
       </c>
       <c r="N58" t="n">
-        <v>70373</v>
+        <v>77494</v>
       </c>
     </row>
     <row r="59">
@@ -3043,13 +3043,13 @@
         <v>57445</v>
       </c>
       <c r="L59" t="n">
-        <v>53354</v>
+        <v>61157</v>
       </c>
       <c r="M59" t="n">
-        <v>15640</v>
+        <v>19373</v>
       </c>
       <c r="N59" t="n">
-        <v>37714</v>
+        <v>41784</v>
       </c>
     </row>
     <row r="60">
@@ -3087,13 +3087,13 @@
         <v>64646</v>
       </c>
       <c r="L60" t="n">
-        <v>91484</v>
+        <v>106780</v>
       </c>
       <c r="M60" t="n">
-        <v>28129</v>
+        <v>35314</v>
       </c>
       <c r="N60" t="n">
-        <v>63355</v>
+        <v>71466</v>
       </c>
     </row>
     <row r="61">
@@ -3131,13 +3131,13 @@
         <v>29176</v>
       </c>
       <c r="L61" t="n">
-        <v>30369</v>
+        <v>33279</v>
       </c>
       <c r="M61" t="n">
-        <v>7828</v>
+        <v>9063</v>
       </c>
       <c r="N61" t="n">
-        <v>22541</v>
+        <v>24216</v>
       </c>
     </row>
     <row r="62">
@@ -3175,13 +3175,13 @@
         <v>25083</v>
       </c>
       <c r="L62" t="n">
-        <v>51137</v>
+        <v>55573</v>
       </c>
       <c r="M62" t="n">
-        <v>8000</v>
+        <v>9502</v>
       </c>
       <c r="N62" t="n">
-        <v>43137</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="63">
@@ -3219,13 +3219,13 @@
         <v>20109</v>
       </c>
       <c r="L63" t="n">
-        <v>30214</v>
+        <v>33317</v>
       </c>
       <c r="M63" t="n">
-        <v>4616</v>
+        <v>5481</v>
       </c>
       <c r="N63" t="n">
-        <v>25598</v>
+        <v>27836</v>
       </c>
     </row>
     <row r="64">
@@ -3263,13 +3263,13 @@
         <v>35709</v>
       </c>
       <c r="L64" t="n">
-        <v>30821</v>
+        <v>34705</v>
       </c>
       <c r="M64" t="n">
-        <v>5930</v>
+        <v>7516</v>
       </c>
       <c r="N64" t="n">
-        <v>24891</v>
+        <v>27189</v>
       </c>
     </row>
     <row r="65">
@@ -3307,13 +3307,13 @@
         <v>69002</v>
       </c>
       <c r="L65" t="n">
-        <v>62227</v>
+        <v>70364</v>
       </c>
       <c r="M65" t="n">
-        <v>13788</v>
+        <v>17183</v>
       </c>
       <c r="N65" t="n">
-        <v>48439</v>
+        <v>53181</v>
       </c>
     </row>
     <row r="66">
@@ -3351,13 +3351,13 @@
         <v>85499</v>
       </c>
       <c r="L66" t="n">
-        <v>66080</v>
+        <v>72339</v>
       </c>
       <c r="M66" t="n">
-        <v>13351</v>
+        <v>15696</v>
       </c>
       <c r="N66" t="n">
-        <v>52729</v>
+        <v>56643</v>
       </c>
     </row>
     <row r="67">
@@ -3395,13 +3395,13 @@
         <v>27583</v>
       </c>
       <c r="L67" t="n">
-        <v>48097</v>
+        <v>54239</v>
       </c>
       <c r="M67" t="n">
-        <v>15272</v>
+        <v>18491</v>
       </c>
       <c r="N67" t="n">
-        <v>32825</v>
+        <v>35748</v>
       </c>
     </row>
     <row r="68">
@@ -3439,13 +3439,13 @@
         <v>42869</v>
       </c>
       <c r="L68" t="n">
-        <v>49330</v>
+        <v>56222</v>
       </c>
       <c r="M68" t="n">
-        <v>10894</v>
+        <v>13244</v>
       </c>
       <c r="N68" t="n">
-        <v>38436</v>
+        <v>42978</v>
       </c>
     </row>
     <row r="69">
@@ -3483,13 +3483,13 @@
         <v>78610</v>
       </c>
       <c r="L69" t="n">
-        <v>70515</v>
+        <v>78079</v>
       </c>
       <c r="M69" t="n">
-        <v>12319</v>
+        <v>14803</v>
       </c>
       <c r="N69" t="n">
-        <v>58196</v>
+        <v>63276</v>
       </c>
     </row>
   </sheetData>
